--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,10 +2810,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,10 +2810,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3007,10 +3007,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,10 +2810,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3007,10 +3007,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4.95</v>
+        <v>1.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7</v>
+        <v>7.55</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.45</v>
+        <v>4.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="R8" t="n">
-        <v>7.55</v>
+        <v>1.7</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,10 +2810,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3007,10 +3007,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.33</v>
+        <v>4.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.69</v>
+        <v>3.22</v>
       </c>
       <c r="R6" t="n">
-        <v>8.75</v>
+        <v>1.7</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="R7" t="n">
-        <v>7.55</v>
+        <v>7.5</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.95</v>
+        <v>1.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.22</v>
+        <v>5.69</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7</v>
+        <v>8.75</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="R9" t="n">
-        <v>7.5</v>
+        <v>7.55</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4.95</v>
+        <v>1.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.22</v>
+        <v>5.69</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7</v>
+        <v>8.75</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="R7" t="n">
-        <v>7.5</v>
+        <v>7.55</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.33</v>
+        <v>4.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.69</v>
+        <v>3.22</v>
       </c>
       <c r="R8" t="n">
-        <v>8.75</v>
+        <v>1.7</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="R9" t="n">
-        <v>7.55</v>
+        <v>7.5</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,10 +2810,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3007,10 +3007,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.69</v>
+        <v>3.55</v>
       </c>
       <c r="R6" t="n">
-        <v>8.75</v>
+        <v>7.55</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.55</v>
+        <v>5.69</v>
       </c>
       <c r="R7" t="n">
-        <v>7.55</v>
+        <v>8.75</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.95</v>
+        <v>1.41</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.22</v>
+        <v>3.85</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7</v>
+        <v>7.5</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.41</v>
+        <v>4.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.85</v>
+        <v>3.22</v>
       </c>
       <c r="R9" t="n">
-        <v>7.5</v>
+        <v>1.7</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="R6" t="n">
-        <v>7.55</v>
+        <v>7.5</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.69</v>
+        <v>3.55</v>
       </c>
       <c r="R7" t="n">
-        <v>8.75</v>
+        <v>7.55</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.41</v>
+        <v>4.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.85</v>
+        <v>3.22</v>
       </c>
       <c r="R8" t="n">
-        <v>7.5</v>
+        <v>1.7</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4.95</v>
+        <v>1.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.22</v>
+        <v>5.69</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7</v>
+        <v>8.75</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="R6" t="n">
-        <v>7.5</v>
+        <v>7.55</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="R7" t="n">
-        <v>7.55</v>
+        <v>7.5</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.95</v>
+        <v>1.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.22</v>
+        <v>5.69</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7</v>
+        <v>8.75</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.33</v>
+        <v>4.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.69</v>
+        <v>3.22</v>
       </c>
       <c r="R9" t="n">
-        <v>8.75</v>
+        <v>1.7</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,10 +2810,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3007,10 +3007,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.85</v>
+        <v>5.69</v>
       </c>
       <c r="R7" t="n">
-        <v>7.5</v>
+        <v>8.75</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.33</v>
+        <v>4.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.69</v>
+        <v>3.22</v>
       </c>
       <c r="R8" t="n">
-        <v>8.75</v>
+        <v>1.7</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4.95</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.22</v>
+        <v>3.85</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7</v>
+        <v>7.5</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.33</v>
+        <v>4.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.69</v>
+        <v>3.22</v>
       </c>
       <c r="R7" t="n">
-        <v>8.75</v>
+        <v>1.7</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.95</v>
+        <v>1.41</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.22</v>
+        <v>3.85</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7</v>
+        <v>7.5</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.85</v>
+        <v>5.69</v>
       </c>
       <c r="R9" t="n">
-        <v>7.5</v>
+        <v>8.75</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,10 +2810,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3007,10 +3007,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI17"/>
+  <dimension ref="A1:BI18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,12 +748,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="BI2" s="3" t="n">
-        <v>46104.47916666666</v>
+        <v>46104.45833333334</v>
       </c>
     </row>
     <row r="3">
@@ -945,7 +945,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
-        <v>46104.54166666666</v>
+        <v>46104.47916666666</v>
       </c>
     </row>
     <row r="4">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>46104.64583333334</v>
+        <v>46104.54166666666</v>
       </c>
     </row>
     <row r="5">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.45</v>
+        <v>2.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="R6" t="n">
-        <v>7.55</v>
+        <v>2.55</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>46104.6875</v>
+        <v>46104.64583333334</v>
       </c>
     </row>
     <row r="7">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="R8" t="n">
-        <v>7.5</v>
+        <v>7.55</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.69</v>
+        <v>3.85</v>
       </c>
       <c r="R9" t="n">
-        <v>8.75</v>
+        <v>7.5</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2324,27 +2324,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.45</v>
+        <v>1.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.15</v>
+        <v>5.69</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6</v>
+        <v>8.75</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46104.75</v>
+        <v>46104.6875</v>
       </c>
     </row>
     <row r="11">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46104.77083333334</v>
+        <v>46104.75</v>
       </c>
     </row>
     <row r="12">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,10 +2810,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46104.79166666666</v>
+        <v>46104.77083333334</v>
       </c>
     </row>
     <row r="13">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3007,10 +3007,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -3112,27 +3112,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46104.85416666666</v>
+        <v>46104.79166666666</v>
       </c>
     </row>
     <row r="15">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46104.875</v>
+        <v>46104.85416666666</v>
       </c>
     </row>
     <row r="16">
@@ -3506,27 +3506,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46104.89583333334</v>
+        <v>46104.875</v>
       </c>
     </row>
     <row r="17">
@@ -3703,27 +3703,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3891,6 +3891,203 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
+        <v>46104.89583333334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Portland Timbers II</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>LA Galaxy II</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" s="3" t="n">
         <v>46104.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4.95</v>
+        <v>1.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7</v>
+        <v>7.55</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.55</v>
+        <v>5.69</v>
       </c>
       <c r="R8" t="n">
-        <v>7.55</v>
+        <v>8.75</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.33</v>
+        <v>4.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.69</v>
+        <v>3.22</v>
       </c>
       <c r="R10" t="n">
-        <v>8.75</v>
+        <v>1.7</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3007,10 +3007,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3204,10 +3204,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="R3" t="n">
-        <v>3.41</v>
+        <v>2.36</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.55</v>
+        <v>5.69</v>
       </c>
       <c r="R7" t="n">
-        <v>7.55</v>
+        <v>8.75</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.69</v>
+        <v>3.85</v>
       </c>
       <c r="R8" t="n">
-        <v>8.75</v>
+        <v>7.5</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.41</v>
+        <v>4.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.85</v>
+        <v>3.22</v>
       </c>
       <c r="R9" t="n">
-        <v>7.5</v>
+        <v>1.7</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4.95</v>
+        <v>1.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7</v>
+        <v>7.55</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3007,10 +3007,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3204,10 +3204,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>7.89</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.69</v>
+        <v>3.55</v>
       </c>
       <c r="R7" t="n">
-        <v>8.75</v>
+        <v>7.55</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4.95</v>
+        <v>1.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.22</v>
+        <v>5.69</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7</v>
+        <v>8.75</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.45</v>
+        <v>4.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="R10" t="n">
-        <v>7.55</v>
+        <v>1.7</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3007,10 +3007,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3204,10 +3204,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1007,13 +1007,13 @@
         <v>2.36</v>
       </c>
       <c r="S3" t="n">
-        <v>3.81</v>
+        <v>3.74</v>
       </c>
       <c r="T3" t="n">
         <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>3.17</v>
+        <v>3.04</v>
       </c>
       <c r="V3" t="n">
         <v>1.49</v>
@@ -1040,10 +1040,10 @@
         <v>1.41</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AF3" t="n">
         <v>1.56</v>
@@ -1067,10 +1067,10 @@
         <v>1.75</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1216,13 +1216,13 @@
         <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="X4" t="n">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z4" t="n">
         <v>6.15</v>
@@ -1234,16 +1234,16 @@
         <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AE4" t="n">
         <v>1.81</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
         <v>2.83</v>
@@ -1252,7 +1252,7 @@
         <v>1.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.62</v>
+        <v>5.25</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.09</v>
@@ -1589,22 +1589,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.75</v>
+        <v>3.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="R6" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="V6" t="n">
         <v>1.42</v>
@@ -1637,10 +1637,10 @@
         <v>1.98</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AH6" t="n">
         <v>1.22</v>
@@ -1652,7 +1652,7 @@
         <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AL6" t="n">
         <v>1.83</v>
@@ -1706,7 +1706,7 @@
         <v>1.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="BD6" t="n">
         <v>3.25</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.55</v>
+        <v>5.69</v>
       </c>
       <c r="R7" t="n">
-        <v>7.55</v>
+        <v>8.75</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.41</v>
+        <v>4.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.85</v>
+        <v>3.22</v>
       </c>
       <c r="R8" t="n">
-        <v>7.5</v>
+        <v>1.7</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.69</v>
+        <v>3.85</v>
       </c>
       <c r="R9" t="n">
-        <v>8.75</v>
+        <v>7.5</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4.95</v>
+        <v>1.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7</v>
+        <v>7.55</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1001,7 +1001,7 @@
         <v>2.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="R3" t="n">
         <v>2.36</v>
@@ -1043,7 +1043,7 @@
         <v>2.52</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AF3" t="n">
         <v>1.56</v>
@@ -1052,7 +1052,7 @@
         <v>4.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AI3" t="n">
         <v>8.300000000000001</v>
@@ -1061,13 +1061,13 @@
         <v>1.01</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="AL3" t="n">
         <v>1.75</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AN3" t="n">
         <v>1.37</v>
@@ -1201,7 +1201,7 @@
         <v>4.7</v>
       </c>
       <c r="R4" t="n">
-        <v>7.89</v>
+        <v>11.5</v>
       </c>
       <c r="S4" t="n">
         <v>1.8</v>
@@ -1219,10 +1219,10 @@
         <v>2.99</v>
       </c>
       <c r="X4" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
         <v>6.15</v>
@@ -1237,13 +1237,13 @@
         <v>1.21</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="AE4" t="n">
         <v>1.81</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG4" t="n">
         <v>2.83</v>
@@ -1252,7 +1252,7 @@
         <v>1.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.25</v>
+        <v>5.62</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.09</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.33</v>
+        <v>4.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.69</v>
+        <v>3.22</v>
       </c>
       <c r="R7" t="n">
-        <v>8.75</v>
+        <v>1.7</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.95</v>
+        <v>1.41</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.22</v>
+        <v>3.85</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7</v>
+        <v>7.5</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="R9" t="n">
-        <v>7.5</v>
+        <v>7.55</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.55</v>
+        <v>5.69</v>
       </c>
       <c r="R10" t="n">
-        <v>7.55</v>
+        <v>8.75</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.85</v>
+        <v>5.69</v>
       </c>
       <c r="R8" t="n">
-        <v>7.5</v>
+        <v>8.75</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.69</v>
+        <v>3.85</v>
       </c>
       <c r="R10" t="n">
-        <v>8.75</v>
+        <v>7.5</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="R11" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,91 +2968,91 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
@@ -3061,13 +3061,13 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
@@ -3076,25 +3076,25 @@
         <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3204,10 +3204,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -3371,40 +3371,40 @@
         <v>4.41</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AE15" t="n">
         <v>1.9</v>
@@ -3413,28 +3413,28 @@
         <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3568,70 +3568,70 @@
         <v>3.22</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1001,7 +1001,7 @@
         <v>2.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="R3" t="n">
         <v>2.36</v>
@@ -1043,10 +1043,10 @@
         <v>2.52</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AG3" t="n">
         <v>4.25</v>
@@ -1061,7 +1061,7 @@
         <v>1.01</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="AL3" t="n">
         <v>1.75</v>
@@ -1198,7 +1198,7 @@
         <v>1.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.7</v>
+        <v>4.72</v>
       </c>
       <c r="R4" t="n">
         <v>11.5</v>
@@ -1252,7 +1252,7 @@
         <v>1.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.62</v>
+        <v>5.25</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.09</v>
@@ -1261,7 +1261,7 @@
         <v>2.06</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AM4" t="n">
         <v>1.04</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="T6" t="n">
         <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>2.81</v>
+        <v>4.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="X6" t="n">
-        <v>3.17</v>
+        <v>2.63</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.9</v>
+        <v>3.48</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.7</v>
+        <v>2.92</v>
       </c>
       <c r="AH6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM6" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AN6" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.31</v>
+        <v>2.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4.95</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.69</v>
+        <v>5.35</v>
       </c>
       <c r="R8" t="n">
-        <v>8.75</v>
+        <v>8</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.55</v>
+        <v>4.75</v>
       </c>
       <c r="R9" t="n">
-        <v>7.55</v>
+        <v>8.76</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
+        <v>6</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI10" t="n">
         <v>7.5</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,91 +2968,91 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
@@ -3061,13 +3061,13 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
@@ -3076,25 +3076,25 @@
         <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,91 +3165,91 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
@@ -3258,13 +3258,13 @@
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
@@ -3273,25 +3273,25 @@
         <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1007,13 +1007,13 @@
         <v>2.36</v>
       </c>
       <c r="S3" t="n">
-        <v>3.74</v>
+        <v>3.81</v>
       </c>
       <c r="T3" t="n">
         <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>3.04</v>
+        <v>3.17</v>
       </c>
       <c r="V3" t="n">
         <v>1.49</v>
@@ -1040,19 +1040,19 @@
         <v>1.41</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="AE3" t="n">
         <v>2.39</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AG3" t="n">
         <v>4.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AI3" t="n">
         <v>8.300000000000001</v>
@@ -1064,25 +1064,25 @@
         <v>1.97</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AM3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN3" t="n">
         <v>1.35</v>
       </c>
-      <c r="AN3" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
@@ -1216,13 +1216,13 @@
         <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="X4" t="n">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z4" t="n">
         <v>6.15</v>
@@ -1240,16 +1240,16 @@
         <v>3.58</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
         <v>2.83</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AI4" t="n">
         <v>5.25</v>
@@ -1267,7 +1267,7 @@
         <v>1.04</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1276,13 +1276,13 @@
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
@@ -1291,13 +1291,13 @@
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
@@ -1733,27 +1733,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,134 +1786,134 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="R7" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="S7" t="n">
-        <v>5.34</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
-        <v>2.47</v>
+        <v>3.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="X7" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.08</v>
       </c>
-      <c r="AC7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AI7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BB7" t="n">
         <v>1.53</v>
       </c>
-      <c r="AG7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ7" t="n">
+      <c r="BC7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BF7" t="n">
         <v>1.05</v>
       </c>
-      <c r="AK7" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BG7" t="n">
         <v>0</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3" t="n">
-        <v>46104.6875</v>
+        <v>46104.66666666666</v>
       </c>
     </row>
     <row r="8">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1986,130 +1986,130 @@
         <v>1.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.35</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>8</v>
+        <v>8.76</v>
       </c>
       <c r="S8" t="n">
         <v>1.75</v>
       </c>
       <c r="T8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="X8" t="n">
         <v>2.63</v>
       </c>
-      <c r="U8" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="Y8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.25</v>
       </c>
-      <c r="W8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="AD8" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE8" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF8" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,80 +2180,80 @@
         </is>
       </c>
       <c r="P9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U9" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R9" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="Z9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN9" t="n">
         <v>2.3</v>
       </c>
-      <c r="U9" t="n">
-        <v>8</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.51</v>
+        <v>4.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>6</v>
+        <v>1.85</v>
       </c>
       <c r="S10" t="n">
-        <v>2.15</v>
+        <v>5.34</v>
       </c>
       <c r="T10" t="n">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>7.07</v>
+        <v>2.47</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="W10" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="X10" t="n">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.68</v>
+        <v>4.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AI10" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AL10" t="n">
         <v>1.62</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.3</v>
+        <v>1.12</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2521,27 +2521,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.37</v>
+        <v>1.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.98</v>
+        <v>5.35</v>
       </c>
       <c r="R11" t="n">
-        <v>2.76</v>
+        <v>8</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="T11" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>6.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>2.31</v>
+        <v>3.6</v>
       </c>
       <c r="X11" t="n">
-        <v>3.34</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.46</v>
+        <v>4.97</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.37</v>
+        <v>1.44</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="AI11" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.36</v>
+        <v>3.19</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.9</v>
+        <v>5.25</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46104.75</v>
+        <v>46104.6875</v>
       </c>
     </row>
     <row r="12">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46104.77083333334</v>
+        <v>46104.75</v>
       </c>
     </row>
     <row r="13">
@@ -2915,27 +2915,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46104.79166666666</v>
+        <v>46104.77083333334</v>
       </c>
     </row>
     <row r="14">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,91 +3165,91 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
@@ -3258,13 +3258,13 @@
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
@@ -3273,25 +3273,25 @@
         <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="R16" t="n">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="S16" t="n">
         <v>2.62</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>8.76</v>
+        <v>1.85</v>
       </c>
       <c r="S8" t="n">
-        <v>1.75</v>
+        <v>5.34</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="U8" t="n">
-        <v>8</v>
+        <v>2.47</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="W8" t="n">
-        <v>2.71</v>
+        <v>2.28</v>
       </c>
       <c r="X8" t="n">
-        <v>2.63</v>
+        <v>3.34</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.15</v>
+        <v>8.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.81</v>
+        <v>2.37</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="AH8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM8" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AN8" t="n">
-        <v>3.3</v>
+        <v>1.12</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="Q9" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="R9" t="n">
+        <v>8</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W9" t="n">
         <v>3.6</v>
       </c>
-      <c r="R9" t="n">
-        <v>6</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="X9" t="n">
         <v>2.15</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U9" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.04</v>
-      </c>
       <c r="Y9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BF9" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.13</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4.6</v>
+        <v>1.51</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.85</v>
+        <v>6</v>
       </c>
       <c r="S10" t="n">
-        <v>5.34</v>
+        <v>2.15</v>
       </c>
       <c r="T10" t="n">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="U10" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W10" t="n">
         <v>2.47</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.28</v>
-      </c>
       <c r="X10" t="n">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AI10" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AL10" t="n">
         <v>1.62</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.12</v>
+        <v>2.3</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2577,130 +2577,130 @@
         <v>1.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.35</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
-        <v>8</v>
+        <v>8.76</v>
       </c>
       <c r="S11" t="n">
         <v>1.75</v>
       </c>
       <c r="T11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>8</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="X11" t="n">
         <v>2.63</v>
       </c>
-      <c r="U11" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="V11" t="n">
+      <c r="Y11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC11" t="n">
         <v>1.25</v>
       </c>
-      <c r="W11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="AD11" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1004,22 +1004,22 @@
         <v>2.83</v>
       </c>
       <c r="R3" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="S3" t="n">
-        <v>3.81</v>
+        <v>3.74</v>
       </c>
       <c r="T3" t="n">
         <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>3.17</v>
+        <v>3.27</v>
       </c>
       <c r="V3" t="n">
         <v>1.49</v>
       </c>
       <c r="W3" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="X3" t="n">
         <v>3.35</v>
@@ -1037,16 +1037,16 @@
         <v>1.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="AE3" t="n">
         <v>2.39</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG3" t="n">
         <v>4.25</v>
@@ -1064,34 +1064,34 @@
         <v>1.97</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.79</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.27</v>
+        <v>2.78</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="AV3" t="n">
         <v>1.92</v>
@@ -1100,16 +1100,16 @@
         <v>1.56</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BB3" t="n">
         <v>1.31</v>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Q4" t="n">
         <v>4.72</v>
@@ -1204,25 +1204,25 @@
         <v>11.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="T4" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>7.95</v>
+        <v>7.4</v>
       </c>
       <c r="V4" t="n">
         <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="X4" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
         <v>6.15</v>
@@ -1240,16 +1240,16 @@
         <v>3.58</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG4" t="n">
         <v>2.83</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AI4" t="n">
         <v>5.25</v>
@@ -1258,37 +1258,37 @@
         <v>1.09</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="AL4" t="n">
         <v>1.66</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="AS4" t="n">
         <v>2.34</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AV4" t="n">
         <v>2.45</v>
@@ -1297,16 +1297,16 @@
         <v>1.88</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="BB4" t="n">
         <v>1.17</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.6</v>
+        <v>1.55</v>
       </c>
       <c r="Q8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BD8" t="n">
         <v>3.1</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>2.9</v>
-      </c>
       <c r="BE8" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2183,130 +2183,130 @@
         <v>1.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.35</v>
+        <v>4.6</v>
       </c>
       <c r="R9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U9" t="n">
         <v>8</v>
       </c>
-      <c r="S9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X9" t="n">
         <v>2.63</v>
       </c>
-      <c r="U9" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="V9" t="n">
+      <c r="Y9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
         <v>1.25</v>
       </c>
-      <c r="W9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.11</v>
-      </c>
       <c r="BC9" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.25</v>
+        <v>3.82</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.51</v>
+        <v>4.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>6</v>
+        <v>1.85</v>
       </c>
       <c r="S10" t="n">
-        <v>2.15</v>
+        <v>5.34</v>
       </c>
       <c r="T10" t="n">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>7.07</v>
+        <v>2.47</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="W10" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="X10" t="n">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.92</v>
+        <v>2.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.68</v>
+        <v>4.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AI10" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AL10" t="n">
         <v>1.62</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2577,130 +2577,130 @@
         <v>1.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>5.35</v>
       </c>
       <c r="R11" t="n">
-        <v>8.76</v>
+        <v>8</v>
       </c>
       <c r="S11" t="n">
         <v>1.75</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="V11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY11" t="n">
         <v>1.37</v>
       </c>
-      <c r="W11" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ11" t="n">
+      <c r="AZ11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB11" t="n">
         <v>1.11</v>
       </c>
-      <c r="AK11" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC11" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1004,13 +1004,13 @@
         <v>2.83</v>
       </c>
       <c r="R3" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="S3" t="n">
-        <v>3.74</v>
+        <v>3.66</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U3" t="n">
         <v>3.27</v>
@@ -1019,7 +1019,7 @@
         <v>1.49</v>
       </c>
       <c r="W3" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="X3" t="n">
         <v>3.35</v>
@@ -1034,10 +1034,10 @@
         <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AD3" t="n">
         <v>2.52</v>
@@ -1046,7 +1046,7 @@
         <v>2.39</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AG3" t="n">
         <v>4.25</v>
@@ -1094,16 +1094,16 @@
         <v>2.51</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AZ3" t="n">
         <v>2.23</v>
@@ -1112,13 +1112,13 @@
         <v>2.06</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BC3" t="n">
         <v>2.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BE3" t="n">
         <v>1.46</v>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Q4" t="n">
         <v>4.72</v>
@@ -1204,70 +1204,70 @@
         <v>11.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="V4" t="n">
         <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="X4" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.15</v>
+        <v>5.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB4" t="n">
         <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AR4" t="n">
         <v>1.83</v>
@@ -1309,19 +1309,19 @@
         <v>5.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>2.15</v>
+        <v>3.83</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="T5" t="n">
         <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>2.75</v>
+        <v>4.61</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="X5" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.7</v>
+        <v>2.92</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.2</v>
       </c>
-      <c r="AI5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC5" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
         <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="X6" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.81</v>
+        <v>2.12</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.92</v>
+        <v>3.7</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q7" t="n">
         <v>2.62</v>
       </c>
       <c r="R7" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="U7" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W7" t="n">
         <v>2.03</v>
       </c>
       <c r="X7" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="Y7" t="n">
         <v>1.15</v>
@@ -1828,7 +1828,7 @@
         <v>1.74</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AE7" t="n">
         <v>3.14</v>
@@ -1837,10 +1837,10 @@
         <v>1.27</v>
       </c>
       <c r="AG7" t="n">
-        <v>6.4</v>
+        <v>6.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AI7" t="n">
         <v>19</v>
@@ -1855,64 +1855,64 @@
         <v>1.45</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.87</v>
+        <v>1.51</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.3</v>
+        <v>2.42</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.81</v>
+        <v>2.34</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>5.35</v>
       </c>
       <c r="R10" t="n">
-        <v>1.85</v>
+        <v>8</v>
       </c>
       <c r="S10" t="n">
-        <v>5.34</v>
+        <v>1.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="U10" t="n">
-        <v>2.47</v>
+        <v>6.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>2.28</v>
+        <v>3.6</v>
       </c>
       <c r="X10" t="n">
-        <v>3.34</v>
+        <v>2.15</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>1.43</v>
       </c>
-      <c r="AD10" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.9</v>
+        <v>5.25</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.35</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>8</v>
+        <v>1.85</v>
       </c>
       <c r="S11" t="n">
-        <v>1.75</v>
+        <v>5.34</v>
       </c>
       <c r="T11" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>6.25</v>
+        <v>2.47</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="W11" t="n">
-        <v>3.6</v>
+        <v>2.28</v>
       </c>
       <c r="X11" t="n">
-        <v>2.15</v>
+        <v>3.34</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AL11" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="AE11" t="n">
+      <c r="AM11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.44</v>
       </c>
-      <c r="AF11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,28 +2771,28 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.37</v>
+        <v>2.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="R12" t="n">
         <v>2.76</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="T12" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="U12" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="V12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W12" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="X12" t="n">
         <v>3.34</v>
@@ -2804,46 +2804,46 @@
         <v>8.699999999999999</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG12" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AI12" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AM12" t="n">
         <v>1.32</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,16 +2885,16 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="BF12" t="n">
         <v>1.1</v>
@@ -2977,70 +2977,70 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3362,19 +3362,19 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>4.41</v>
+        <v>4.82</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="U15" t="n">
         <v>4.6</v>
@@ -3386,7 +3386,7 @@
         <v>2.38</v>
       </c>
       <c r="X15" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="Y15" t="n">
         <v>1.35</v>
@@ -3398,31 +3398,31 @@
         <v>1.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AD15" t="n">
         <v>3.05</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AG15" t="n">
         <v>3.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" t="n">
         <v>7</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK15" t="n">
         <v>1.85</v>
@@ -3479,7 +3479,7 @@
         <v>1.22</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="BD15" t="n">
         <v>3.5</v>
@@ -3559,19 +3559,19 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="T16" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="U16" t="n">
         <v>5.4</v>
@@ -3580,19 +3580,19 @@
         <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>2.68</v>
+        <v>2.24</v>
       </c>
       <c r="X16" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AB16" t="n">
         <v>1.05</v>
@@ -3604,16 +3604,16 @@
         <v>2.74</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.78</v>
+        <v>3.96</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AI16" t="n">
         <v>7.7</v>
@@ -3622,10 +3622,10 @@
         <v>1.02</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AM16" t="n">
         <v>1.34</v>
@@ -3637,52 +3637,52 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BD16" t="n">
         <v>3.28</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BF16" t="n">
         <v>1.1</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>3.83</v>
+        <v>2.15</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4</v>
+        <v>3.85</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.61</v>
+        <v>2.83</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.92</v>
+        <v>3.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>2.15</v>
+        <v>3.83</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="T6" t="n">
         <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>2.75</v>
+        <v>4.61</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="X6" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.7</v>
+        <v>2.92</v>
       </c>
       <c r="AH6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
         <v>1.2</v>
       </c>
-      <c r="AI6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC6" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.7</v>
+        <v>5.35</v>
       </c>
       <c r="R8" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="S8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X8" t="n">
         <v>2.15</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U8" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.04</v>
-      </c>
       <c r="Y8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BF8" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.13</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2183,16 +2183,16 @@
         <v>1.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="R9" t="n">
-        <v>8.5</v>
+        <v>8.76</v>
       </c>
       <c r="S9" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="T9" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
         <v>8</v>
@@ -2204,55 +2204,55 @@
         <v>2.95</v>
       </c>
       <c r="X9" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
         <v>6.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AE9" t="n">
         <v>1.81</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AI9" t="n">
         <v>5.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AM9" t="n">
         <v>1.05</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2297,16 +2297,16 @@
         <v>1.25</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.35</v>
+        <v>2.91</v>
       </c>
       <c r="R10" t="n">
-        <v>8</v>
+        <v>1.85</v>
       </c>
       <c r="S10" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM10" t="n">
         <v>1.75</v>
       </c>
-      <c r="T10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U10" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="AE10" t="n">
+      <c r="AN10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.44</v>
       </c>
-      <c r="AF10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF10" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>4.6</v>
+        <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.85</v>
+        <v>6.2</v>
       </c>
       <c r="S11" t="n">
-        <v>5.34</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
-        <v>2.47</v>
+        <v>7.55</v>
       </c>
       <c r="V11" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>2.28</v>
+        <v>2.67</v>
       </c>
       <c r="X11" t="n">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.06</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.01</v>
       </c>
       <c r="AK11" t="n">
         <v>2.13</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -3046,34 +3046,34 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3559,40 +3559,40 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="T16" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="U16" t="n">
         <v>5.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="W16" t="n">
         <v>2.24</v>
       </c>
       <c r="X16" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
         <v>8.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AB16" t="n">
         <v>1.05</v>
@@ -3601,19 +3601,19 @@
         <v>1.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.74</v>
+        <v>3.07</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AI16" t="n">
         <v>7.7</v>
@@ -3622,10 +3622,10 @@
         <v>1.02</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AM16" t="n">
         <v>1.34</v>
@@ -3637,43 +3637,43 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AT16" t="n">
         <v>2.7</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AY16" t="n">
         <v>1.31</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.78</v>
+        <v>3.48</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC16" t="n">
         <v>2.26</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1013,7 +1013,7 @@
         <v>1.93</v>
       </c>
       <c r="U3" t="n">
-        <v>3.27</v>
+        <v>3.12</v>
       </c>
       <c r="V3" t="n">
         <v>1.49</v>
@@ -1040,7 +1040,7 @@
         <v>1.41</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="AE3" t="n">
         <v>2.39</v>
@@ -1052,7 +1052,7 @@
         <v>4.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AI3" t="n">
         <v>8.300000000000001</v>
@@ -1064,13 +1064,13 @@
         <v>1.97</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AM3" t="n">
         <v>1.35</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>2.51</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AW3" t="n">
         <v>1.54</v>
@@ -1195,67 +1195,67 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.72</v>
+        <v>4.6</v>
       </c>
       <c r="R4" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="S4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="V4" t="n">
         <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="X4" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB4" t="n">
         <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AI4" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK4" t="n">
         <v>2.07</v>
@@ -1264,10 +1264,10 @@
         <v>1.71</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1279,10 +1279,10 @@
         <v>1.46</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AT4" t="n">
         <v>3.11</v>
@@ -1291,10 +1291,10 @@
         <v>3.37</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AX4" t="n">
         <v>1.52</v>
@@ -1309,19 +1309,19 @@
         <v>5.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
         <v>3.85</v>
@@ -1407,25 +1407,25 @@
         <v>2.05</v>
       </c>
       <c r="U5" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="V5" t="n">
         <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="X5" t="n">
         <v>3.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
         <v>8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
         <v>1.06</v>
@@ -1434,19 +1434,19 @@
         <v>1.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG5" t="n">
         <v>3.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI5" t="n">
         <v>6.4</v>
@@ -1455,13 +1455,13 @@
         <v>1.03</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AL5" t="n">
         <v>1.85</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
         <v>1.3</v>
@@ -1485,13 +1485,13 @@
         <v>3.32</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="AV5" t="n">
         <v>2.28</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AX5" t="n">
         <v>1.49</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q8" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="R8" t="n">
-        <v>8</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U8" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AG8" t="n">
-        <v>2.35</v>
+        <v>3.58</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.93</v>
+        <v>1.59</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AN8" t="n">
-        <v>3.19</v>
+        <v>2.3</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.25</v>
+        <v>3.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T11" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>7.55</v>
+        <v>6.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>2.67</v>
+        <v>3.66</v>
       </c>
       <c r="X11" t="n">
-        <v>3.04</v>
+        <v>2.34</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.1</v>
+        <v>4.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.92</v>
+        <v>4.97</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.58</v>
+        <v>2.27</v>
       </c>
       <c r="AH11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.21</v>
       </c>
-      <c r="AI11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK11" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.59</v>
+        <v>1.93</v>
       </c>
       <c r="AM11" t="n">
         <v>1.1</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="BB11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BF11" t="n">
         <v>1.3</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.13</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1001,16 +1001,16 @@
         <v>2.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>2.33</v>
+        <v>3.38</v>
       </c>
       <c r="S3" t="n">
         <v>3.66</v>
       </c>
       <c r="T3" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="U3" t="n">
         <v>3.12</v>
@@ -1040,7 +1040,7 @@
         <v>1.41</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="AE3" t="n">
         <v>2.39</v>
@@ -1082,10 +1082,10 @@
         <v>1.79</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.78</v>
+        <v>2.29</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AT3" t="n">
         <v>4.52</v>
@@ -1094,7 +1094,7 @@
         <v>2.51</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AW3" t="n">
         <v>1.54</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.6</v>
+        <v>4.72</v>
       </c>
       <c r="R4" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="S4" t="n">
         <v>1.78</v>
@@ -1210,10 +1210,10 @@
         <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>7.4</v>
+        <v>8.06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
         <v>3.16</v>
@@ -1240,13 +1240,13 @@
         <v>3.94</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AF4" t="n">
         <v>2.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="AH4" t="n">
         <v>1.41</v>
@@ -1255,7 +1255,7 @@
         <v>4.75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK4" t="n">
         <v>2.07</v>
@@ -1264,7 +1264,7 @@
         <v>1.71</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AN4" t="n">
         <v>3.2</v>
@@ -1294,7 +1294,7 @@
         <v>2.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AX4" t="n">
         <v>1.52</v>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q7" t="n">
         <v>2.62</v>
@@ -1798,16 +1798,16 @@
         <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="W7" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="X7" t="n">
         <v>4.3</v>
@@ -1816,7 +1816,7 @@
         <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA7" t="n">
         <v>1.03</v>
@@ -1825,10 +1825,10 @@
         <v>1.17</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>3.14</v>
@@ -1840,10 +1840,10 @@
         <v>6.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AI7" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AJ7" t="n">
         <v>1.02</v>
@@ -1852,13 +1852,13 @@
         <v>2.45</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AM7" t="n">
         <v>1.41</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
         <v>1.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AS7" t="n">
         <v>3.42</v>
@@ -1885,7 +1885,7 @@
         <v>1.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AX7" t="n">
         <v>1.23</v>
@@ -1894,25 +1894,25 @@
         <v>1.08</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="BA7" t="n">
         <v>2.05</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="R9" t="n">
-        <v>8.76</v>
+        <v>7.4</v>
       </c>
       <c r="S9" t="n">
         <v>1.75</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="U9" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>2.95</v>
+        <v>3.66</v>
       </c>
       <c r="X9" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.15</v>
+        <v>4.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>1.23</v>
       </c>
-      <c r="AD9" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ9" t="n">
+      <c r="BA9" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="BB9" t="n">
         <v>1.11</v>
       </c>
-      <c r="AK9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC9" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.91</v>
+        <v>4.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.85</v>
+        <v>8.76</v>
       </c>
       <c r="S10" t="n">
-        <v>5.34</v>
+        <v>1.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>2.47</v>
+        <v>8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>2.28</v>
+        <v>2.95</v>
       </c>
       <c r="X10" t="n">
-        <v>3.34</v>
+        <v>2.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.6</v>
+        <v>6.15</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC10" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.5</v>
+        <v>3.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.37</v>
+        <v>1.81</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.35</v>
+        <v>2.97</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="AJ10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM10" t="n">
         <v>1.05</v>
       </c>
-      <c r="AK10" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AL10" t="n">
+      <c r="AN10" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.62</v>
       </c>
-      <c r="AM10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BF10" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.37</v>
+        <v>4.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>2.91</v>
       </c>
       <c r="R11" t="n">
-        <v>7.4</v>
+        <v>1.85</v>
       </c>
       <c r="S11" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM11" t="n">
         <v>1.75</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="AE11" t="n">
+      <c r="AN11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.44</v>
       </c>
-      <c r="AF11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM11" t="n">
+      <c r="BF11" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.3</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.51</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="R12" t="n">
         <v>2.76</v>
       </c>
       <c r="S12" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="U12" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="W12" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="X12" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AC12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.44</v>
       </c>
-      <c r="AD12" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AG12" t="n">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AH12" t="n">
         <v>1.14</v>
       </c>
       <c r="AI12" t="n">
-        <v>8.699999999999999</v>
+        <v>12</v>
       </c>
       <c r="AJ12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF12" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2977,10 +2977,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="T13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U13" t="n">
         <v>4.6</v>
@@ -2992,7 +2992,7 @@
         <v>2.11</v>
       </c>
       <c r="X13" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="Y13" t="n">
         <v>1.16</v>
@@ -3007,19 +3007,19 @@
         <v>1.08</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AG13" t="n">
-        <v>6.1</v>
+        <v>5.94</v>
       </c>
       <c r="AH13" t="n">
         <v>1.06</v>
@@ -3028,16 +3028,16 @@
         <v>13.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AN13" t="n">
         <v>1.59</v>
@@ -3076,22 +3076,22 @@
         <v>1.25</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB13" t="n">
         <v>1.39</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="BD13" t="n">
         <v>2.66</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BF13" t="n">
         <v>1.02</v>
@@ -3362,58 +3362,58 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
         <v>4.82</v>
       </c>
       <c r="S15" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
         <v>4.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W15" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X15" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.75</v>
+        <v>6.95</v>
       </c>
       <c r="AA15" t="n">
         <v>1.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AH15" t="n">
         <v>1.25</v>
@@ -3434,7 +3434,7 @@
         <v>1.3</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3559,19 +3559,19 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q16" t="n">
         <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="S16" t="n">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="T16" t="n">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="U16" t="n">
         <v>5.4</v>
@@ -3583,13 +3583,13 @@
         <v>2.24</v>
       </c>
       <c r="X16" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="Y16" t="n">
         <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>1.01</v>
@@ -3601,16 +3601,16 @@
         <v>1.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.07</v>
+        <v>2.74</v>
       </c>
       <c r="AE16" t="n">
         <v>2.24</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="AH16" t="n">
         <v>1.19</v>
@@ -3640,7 +3640,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AR16" t="n">
         <v>2</v>
@@ -3649,10 +3649,10 @@
         <v>2.23</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="AV16" t="n">
         <v>2.5</v>
@@ -3667,13 +3667,13 @@
         <v>1.31</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC16" t="n">
         <v>2.26</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -998,19 +998,19 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.47</v>
+        <v>2.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="R3" t="n">
-        <v>3.38</v>
+        <v>2.45</v>
       </c>
       <c r="S3" t="n">
         <v>3.66</v>
       </c>
       <c r="T3" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="U3" t="n">
         <v>3.12</v>
@@ -1040,10 +1040,10 @@
         <v>1.41</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AF3" t="n">
         <v>1.59</v>
@@ -1064,7 +1064,7 @@
         <v>1.97</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AM3" t="n">
         <v>1.35</v>
@@ -1076,13 +1076,13 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.79</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.29</v>
+        <v>2.78</v>
       </c>
       <c r="AS3" t="n">
         <v>3.1</v>
@@ -1106,7 +1106,7 @@
         <v>1.12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="BA3" t="n">
         <v>2.06</v>
@@ -1195,22 +1195,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Q4" t="n">
         <v>4.72</v>
       </c>
       <c r="R4" t="n">
-        <v>11.5</v>
+        <v>8.25</v>
       </c>
       <c r="S4" t="n">
         <v>1.78</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="U4" t="n">
-        <v>8.06</v>
+        <v>7.4</v>
       </c>
       <c r="V4" t="n">
         <v>1.3</v>
@@ -1219,7 +1219,7 @@
         <v>3.16</v>
       </c>
       <c r="X4" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="Y4" t="n">
         <v>1.47</v>
@@ -1249,7 +1249,7 @@
         <v>2.62</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AI4" t="n">
         <v>4.75</v>
@@ -1258,10 +1258,10 @@
         <v>1.12</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AM4" t="n">
         <v>1.17</v>
@@ -1276,10 +1276,10 @@
         <v>1.24</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AS4" t="n">
         <v>2.32</v>
@@ -1294,7 +1294,7 @@
         <v>2.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AX4" t="n">
         <v>1.52</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T5" t="n">
         <v>2.1</v>
       </c>
-      <c r="S5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.05</v>
-      </c>
       <c r="U5" t="n">
-        <v>2.89</v>
+        <v>4.65</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="X5" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.9</v>
+        <v>3.48</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.45</v>
+        <v>2.92</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM5" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AN5" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="R6" t="n">
-        <v>3.83</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>3.85</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U6" t="n">
-        <v>4.61</v>
+        <v>2.89</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="X6" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD6" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH6" t="n">
+      <c r="AI6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM6" t="n">
         <v>1.31</v>
       </c>
-      <c r="AI6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AN6" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T8" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="U8" t="n">
-        <v>7.55</v>
+        <v>6.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>2.67</v>
+        <v>3.66</v>
       </c>
       <c r="X8" t="n">
-        <v>3.04</v>
+        <v>2.34</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.1</v>
+        <v>4.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.92</v>
+        <v>4.97</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.58</v>
+        <v>2.27</v>
       </c>
       <c r="AH8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.21</v>
       </c>
-      <c r="AI8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK8" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.59</v>
+        <v>1.93</v>
       </c>
       <c r="AM8" t="n">
         <v>1.1</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="BB8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BF8" t="n">
         <v>1.3</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.13</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.37</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.75</v>
+        <v>2.91</v>
       </c>
       <c r="R9" t="n">
-        <v>7.4</v>
+        <v>1.85</v>
       </c>
       <c r="S9" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM9" t="n">
         <v>1.75</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="AN9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.44</v>
       </c>
-      <c r="AF9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM9" t="n">
+      <c r="BF9" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.3</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,80 +2377,80 @@
         </is>
       </c>
       <c r="P10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="R10" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T10" t="n">
+      <c r="Z10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN10" t="n">
         <v>2.3</v>
       </c>
-      <c r="U10" t="n">
-        <v>8</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>3.08</v>
-      </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.91</v>
+        <v>4.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.85</v>
+        <v>8.76</v>
       </c>
       <c r="S11" t="n">
-        <v>5.34</v>
+        <v>1.75</v>
       </c>
       <c r="T11" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>2.47</v>
+        <v>8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>2.28</v>
+        <v>2.95</v>
       </c>
       <c r="X11" t="n">
-        <v>3.34</v>
+        <v>2.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.6</v>
+        <v>6.15</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC11" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.5</v>
+        <v>3.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.37</v>
+        <v>1.81</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.35</v>
+        <v>2.97</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="AJ11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM11" t="n">
         <v>1.05</v>
       </c>
-      <c r="AK11" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AL11" t="n">
+      <c r="AN11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.62</v>
       </c>
-      <c r="AM11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>2.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="R5" t="n">
-        <v>3.83</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="U5" t="n">
-        <v>4.65</v>
+        <v>2.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.2</v>
+        <v>7.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.48</v>
+        <v>3.04</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.92</v>
+        <v>3.9</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T6" t="n">
         <v>2.1</v>
       </c>
-      <c r="S6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.05</v>
-      </c>
       <c r="U6" t="n">
-        <v>2.89</v>
+        <v>4.65</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="X6" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.9</v>
+        <v>3.48</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.45</v>
+        <v>2.92</v>
       </c>
       <c r="AH6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM6" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AN6" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.37</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>7.4</v>
+        <v>1.87</v>
       </c>
       <c r="S8" t="n">
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.63</v>
+        <v>1.82</v>
       </c>
       <c r="U8" t="n">
-        <v>6.5</v>
+        <v>2.54</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="W8" t="n">
-        <v>3.66</v>
+        <v>2.22</v>
       </c>
       <c r="X8" t="n">
-        <v>2.34</v>
+        <v>3.34</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.75</v>
+        <v>8.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AC8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.17</v>
       </c>
-      <c r="AD8" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="AI8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE8" t="n">
         <v>1.44</v>
       </c>
-      <c r="AF8" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2.07</v>
-      </c>
       <c r="BF8" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.91</v>
+        <v>4.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.85</v>
+        <v>7.54</v>
       </c>
       <c r="S9" t="n">
-        <v>5.34</v>
+        <v>1.77</v>
       </c>
       <c r="T9" t="n">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>2.47</v>
+        <v>6.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>2.28</v>
+        <v>3.7</v>
       </c>
       <c r="X9" t="n">
-        <v>3.34</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.37</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.44</v>
+        <v>2.45</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.35</v>
+        <v>2.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.14</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" t="n">
-        <v>8.5</v>
+        <v>3.95</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR9" t="n">
         <v>2.13</v>
       </c>
-      <c r="AL9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.47</v>
+        <v>1.71</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="R10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -2392,58 +2392,58 @@
         <v>2.15</v>
       </c>
       <c r="U10" t="n">
-        <v>7.55</v>
+        <v>7.34</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="X10" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
         <v>1.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AE10" t="n">
         <v>2.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AI10" t="n">
         <v>7.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AM10" t="n">
         <v>1.1</v>
@@ -2494,7 +2494,7 @@
         <v>1.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="BD10" t="n">
         <v>3.1</v>
@@ -2503,7 +2503,7 @@
         <v>1.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.9</v>
+        <v>5.21</v>
       </c>
       <c r="R11" t="n">
-        <v>8.76</v>
+        <v>8.5</v>
       </c>
       <c r="S11" t="n">
         <v>1.75</v>
@@ -2592,10 +2592,10 @@
         <v>8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="X11" t="n">
         <v>2.6</v>
@@ -2604,49 +2604,49 @@
         <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
         <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AH11" t="n">
         <v>1.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AJ11" t="n">
         <v>1.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2700,7 +2700,7 @@
         <v>1.62</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI18"/>
+  <dimension ref="A1:BI20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,12 +748,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="BI2" s="3" t="n">
-        <v>46104.45833333334</v>
+        <v>46104.4375</v>
       </c>
     </row>
     <row r="3">
@@ -945,12 +945,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
-        <v>46104.47916666666</v>
+        <v>46104.45833333334</v>
       </c>
     </row>
     <row r="4">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,134 +1195,134 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.29</v>
+        <v>2.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.72</v>
+        <v>2.83</v>
       </c>
       <c r="R4" t="n">
-        <v>8.25</v>
+        <v>2.45</v>
       </c>
       <c r="S4" t="n">
-        <v>1.78</v>
+        <v>3.66</v>
       </c>
       <c r="T4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W4" t="n">
         <v>2.41</v>
       </c>
-      <c r="U4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.16</v>
-      </c>
       <c r="X4" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF4" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>46104.54166666666</v>
+        <v>46104.47916666666</v>
       </c>
     </row>
     <row r="5">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.77</v>
+        <v>1.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.13</v>
+        <v>4.72</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>8.25</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8</v>
+        <v>1.78</v>
       </c>
       <c r="T5" t="n">
-        <v>1.97</v>
+        <v>2.41</v>
       </c>
       <c r="U5" t="n">
-        <v>2.6</v>
+        <v>7.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X5" t="n">
         <v>2.56</v>
       </c>
-      <c r="X5" t="n">
-        <v>3.05</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.9</v>
+        <v>5.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.04</v>
+        <v>3.94</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.9</v>
+        <v>2.62</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.4</v>
+        <v>4.75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.3</v>
+        <v>3.12</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.9</v>
+        <v>3.37</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.46</v>
+        <v>1.16</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.86</v>
+        <v>5.95</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
-        <v>46104.64583333334</v>
+        <v>46104.54166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>2.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="R6" t="n">
-        <v>3.83</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="U6" t="n">
-        <v>4.65</v>
+        <v>2.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="X6" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.2</v>
+        <v>7.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.48</v>
+        <v>3.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.92</v>
+        <v>3.9</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3" t="n">
-        <v>46104.66666666666</v>
+        <v>46104.64583333334</v>
       </c>
     </row>
     <row r="8">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.87</v>
+        <v>3.83</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>2.54</v>
+        <v>4.65</v>
       </c>
       <c r="V8" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>2.22</v>
+        <v>2.83</v>
       </c>
       <c r="X8" t="n">
-        <v>3.34</v>
+        <v>2.63</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC8" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.25</v>
+        <v>2.92</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AI8" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.11</v>
+        <v>1.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.6</v>
+        <v>1.96</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AN8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
         <v>1.2</v>
       </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BC8" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="BI8" s="3" t="n">
-        <v>46104.6875</v>
+        <v>46104.64583333334</v>
       </c>
     </row>
     <row r="9">
@@ -2127,27 +2127,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7.54</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
-        <v>46104.6875</v>
+        <v>46104.66666666666</v>
       </c>
     </row>
     <row r="10">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.85</v>
+        <v>5.21</v>
       </c>
       <c r="R10" t="n">
-        <v>6.4</v>
+        <v>8.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T10" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>7.34</v>
+        <v>8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>2.53</v>
+        <v>2.97</v>
       </c>
       <c r="X10" t="n">
-        <v>2.97</v>
+        <v>2.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="AJ10" t="n">
         <v>1.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.62</v>
       </c>
-      <c r="AM10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BF10" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.26</v>
+        <v>4.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.21</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z11" t="n">
         <v>8.5</v>
       </c>
-      <c r="S11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>8</v>
-      </c>
-      <c r="V11" t="n">
+      <c r="AA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM11" t="n">
         <v>1.31</v>
       </c>
-      <c r="W11" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH11" t="n">
+      <c r="AN11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC11" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2718,27 +2718,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.41</v>
+        <v>1.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.92</v>
+        <v>3.85</v>
       </c>
       <c r="R12" t="n">
-        <v>2.76</v>
+        <v>6.4</v>
       </c>
       <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U12" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD12" t="n">
         <v>3.1</v>
       </c>
-      <c r="T12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="BE12" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BF12" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46104.75</v>
+        <v>46104.6875</v>
       </c>
     </row>
     <row r="13">
@@ -2915,27 +2915,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,134 +2968,134 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>7.54</v>
       </c>
       <c r="S13" t="n">
-        <v>3.02</v>
+        <v>1.77</v>
       </c>
       <c r="T13" t="n">
-        <v>1.76</v>
+        <v>2.62</v>
       </c>
       <c r="U13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BD13" t="n">
         <v>4.6</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="X13" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY13" t="n">
+      <c r="BE13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.25</v>
       </c>
-      <c r="AZ13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.02</v>
-      </c>
       <c r="BG13" t="n">
         <v>0</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46104.77083333334</v>
+        <v>46104.6875</v>
       </c>
     </row>
     <row r="14">
@@ -3112,27 +3112,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46104.79166666666</v>
+        <v>46104.75</v>
       </c>
     </row>
     <row r="15">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46104.85416666666</v>
+        <v>46104.77083333334</v>
       </c>
     </row>
     <row r="16">
@@ -3506,27 +3506,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46104.875</v>
+        <v>46104.79166666666</v>
       </c>
     </row>
     <row r="17">
@@ -3703,27 +3703,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46104.89583333334</v>
+        <v>46104.85416666666</v>
       </c>
     </row>
     <row r="18">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4088,6 +4088,400 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
+        <v>46104.875</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Mount Pleasant Academy FC</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Portmore United</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" s="3" t="n">
+        <v>46104.89583333334</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Portland Timbers II</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>LA Galaxy II</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" s="3" t="n">
         <v>46104.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1216,7 +1216,7 @@
         <v>1.49</v>
       </c>
       <c r="W4" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="X4" t="n">
         <v>3.35</v>
@@ -1237,13 +1237,13 @@
         <v>1.41</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG4" t="n">
         <v>4.25</v>
@@ -1285,10 +1285,10 @@
         <v>3.1</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="AV4" t="n">
         <v>1.92</v>
@@ -1297,10 +1297,10 @@
         <v>1.54</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AZ4" t="n">
         <v>2.17</v>
@@ -1395,10 +1395,10 @@
         <v>1.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.72</v>
+        <v>4.35</v>
       </c>
       <c r="R5" t="n">
-        <v>8.25</v>
+        <v>7.1</v>
       </c>
       <c r="S5" t="n">
         <v>1.78</v>
@@ -1416,7 +1416,7 @@
         <v>3.16</v>
       </c>
       <c r="X5" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="Y5" t="n">
         <v>1.47</v>
@@ -1437,7 +1437,7 @@
         <v>3.94</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AF5" t="n">
         <v>2.15</v>
@@ -1455,16 +1455,16 @@
         <v>1.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AL5" t="n">
         <v>1.71</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.21</v>
+        <v>4.6</v>
       </c>
       <c r="R10" t="n">
-        <v>8.5</v>
+        <v>7.54</v>
       </c>
       <c r="S10" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>2.97</v>
+        <v>3.7</v>
       </c>
       <c r="X10" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF10" t="n">
+      <c r="AQ10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.91</v>
       </c>
-      <c r="AG10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
+      <c r="BF10" t="n">
         <v>1.25</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U11" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD11" t="n">
         <v>3.1</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="S11" t="n">
-        <v>6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>2.9</v>
-      </c>
       <c r="BE11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.85</v>
+        <v>5.21</v>
       </c>
       <c r="R12" t="n">
-        <v>6.4</v>
+        <v>8.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>7.34</v>
+        <v>8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>2.53</v>
+        <v>2.97</v>
       </c>
       <c r="X12" t="n">
-        <v>2.97</v>
+        <v>2.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.62</v>
       </c>
-      <c r="AM12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BF12" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>7.54</v>
+        <v>1.87</v>
       </c>
       <c r="S13" t="n">
-        <v>1.77</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.62</v>
+        <v>1.82</v>
       </c>
       <c r="U13" t="n">
-        <v>6.5</v>
+        <v>2.54</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="W13" t="n">
-        <v>3.7</v>
+        <v>2.22</v>
       </c>
       <c r="X13" t="n">
-        <v>2.2</v>
+        <v>3.34</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.75</v>
+        <v>8.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.45</v>
+        <v>1.52</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.35</v>
+        <v>4.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.77</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T6" t="n">
         <v>2.1</v>
       </c>
-      <c r="S6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.97</v>
-      </c>
       <c r="U6" t="n">
-        <v>2.6</v>
+        <v>4.61</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="X6" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.9</v>
+        <v>6.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.04</v>
+        <v>3.48</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.9</v>
+        <v>2.92</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>7.54</v>
+        <v>1.87</v>
       </c>
       <c r="S10" t="n">
-        <v>1.77</v>
+        <v>6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>6.5</v>
+        <v>2.54</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
-        <v>3.7</v>
+        <v>2.22</v>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>3.34</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.75</v>
+        <v>8.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.45</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.35</v>
+        <v>4.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.85</v>
+        <v>5.21</v>
       </c>
       <c r="R11" t="n">
-        <v>6.4</v>
+        <v>8.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T11" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>7.34</v>
+        <v>8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>2.53</v>
+        <v>2.97</v>
       </c>
       <c r="X11" t="n">
-        <v>2.97</v>
+        <v>2.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="AJ11" t="n">
         <v>1.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.62</v>
       </c>
-      <c r="AM11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.21</v>
+        <v>4.6</v>
       </c>
       <c r="R12" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="S12" t="n">
         <v>1.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="U12" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>2.97</v>
+        <v>3.66</v>
       </c>
       <c r="X12" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF12" t="n">
+      <c r="AQ12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.91</v>
       </c>
-      <c r="AG12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.62</v>
-      </c>
       <c r="BF12" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U13" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD13" t="n">
         <v>3.1</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="S13" t="n">
-        <v>6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>2.9</v>
-      </c>
       <c r="BE13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1216,7 +1216,7 @@
         <v>1.49</v>
       </c>
       <c r="W4" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="X4" t="n">
         <v>3.35</v>
@@ -1237,13 +1237,13 @@
         <v>1.41</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG4" t="n">
         <v>4.25</v>
@@ -1282,25 +1282,25 @@
         <v>2.78</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="AV4" t="n">
         <v>1.92</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AX4" t="n">
         <v>1.27</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AZ4" t="n">
         <v>2.17</v>
@@ -1392,16 +1392,16 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.35</v>
+        <v>4.72</v>
       </c>
       <c r="R5" t="n">
-        <v>7.1</v>
+        <v>8.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="T5" t="n">
         <v>2.41</v>
@@ -1434,13 +1434,13 @@
         <v>1.17</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.94</v>
+        <v>4.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AG5" t="n">
         <v>2.62</v>
@@ -1458,7 +1458,7 @@
         <v>2.01</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AM5" t="n">
         <v>1.17</v>
@@ -1598,7 +1598,7 @@
         <v>3.83</v>
       </c>
       <c r="S6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T6" t="n">
         <v>2.1</v>
@@ -1628,10 +1628,10 @@
         <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AE6" t="n">
         <v>1.81</v>
@@ -1640,10 +1640,10 @@
         <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" t="n">
         <v>5.7</v>
@@ -1658,10 +1658,10 @@
         <v>1.96</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
         <v>3.8</v>
@@ -2067,7 +2067,7 @@
         <v>1.54</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AS8" t="n">
         <v>2.44</v>
@@ -2076,7 +2076,7 @@
         <v>3.32</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="AV8" t="n">
         <v>2.28</v>
@@ -2183,19 +2183,19 @@
         <v>3.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="n">
         <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>4.72</v>
       </c>
       <c r="T9" t="n">
         <v>1.8</v>
       </c>
       <c r="U9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
         <v>1.78</v>
@@ -2210,31 +2210,31 @@
         <v>1.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
         <v>1.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.35</v>
+        <v>7.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AI9" t="n">
         <v>14</v>
@@ -2243,16 +2243,16 @@
         <v>1.02</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AL9" t="n">
         <v>1.5</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2264,16 +2264,16 @@
         <v>1.9</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="AT9" t="n">
         <v>5.12</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AV9" t="n">
         <v>1.8</v>
@@ -2282,22 +2282,22 @@
         <v>1.46</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AY9" t="n">
         <v>1.08</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="BB9" t="n">
         <v>1.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="BD9" t="n">
         <v>2.4</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>1.29</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.87</v>
+        <v>8.4</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>1.74</v>
       </c>
       <c r="T10" t="n">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>2.54</v>
+        <v>8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>2.22</v>
+        <v>2.97</v>
       </c>
       <c r="X10" t="n">
-        <v>3.34</v>
+        <v>2.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.5</v>
+        <v>6.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.93</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="AI10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.2</v>
+        <v>3.08</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.26</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.21</v>
+        <v>2.91</v>
       </c>
       <c r="R11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z11" t="n">
         <v>8.5</v>
       </c>
-      <c r="S11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>8</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AA11" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>1.51</v>
       </c>
       <c r="AG11" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="AH11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC11" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="R12" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="U12" t="n">
-        <v>6.5</v>
+        <v>7.34</v>
       </c>
       <c r="V12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.22</v>
       </c>
-      <c r="W12" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI12" t="n">
-        <v>3.95</v>
+        <v>7.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AM12" t="n">
         <v>1.1</v>
       </c>
       <c r="AN12" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.85</v>
+        <v>4.55</v>
       </c>
       <c r="R13" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="T13" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="U13" t="n">
-        <v>7.34</v>
+        <v>6.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>2.53</v>
+        <v>3.66</v>
       </c>
       <c r="X13" t="n">
-        <v>2.97</v>
+        <v>2.18</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>8</v>
+        <v>4.75</v>
       </c>
       <c r="AA13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AC13" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.9</v>
+        <v>5.05</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.69</v>
+        <v>2.45</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.8</v>
+        <v>2.35</v>
       </c>
       <c r="AH13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AK13" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.38</v>
+        <v>1.71</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,19 +3165,19 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="R14" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="T14" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>3.5</v>
@@ -3204,31 +3204,31 @@
         <v>1.07</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
         <v>1.44</v>
       </c>
       <c r="AG14" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AH14" t="n">
         <v>1.14</v>
       </c>
       <c r="AI14" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AL14" t="n">
         <v>1.67</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BE14" t="n">
         <v>1.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3371,124 +3371,124 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3756,16 +3756,16 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="T17" t="n">
         <v>2.2</v>
@@ -3774,46 +3774,46 @@
         <v>4.6</v>
       </c>
       <c r="V17" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="W17" t="n">
-        <v>2.36</v>
+        <v>2.71</v>
       </c>
       <c r="X17" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD17" t="n">
         <v>2.88</v>
       </c>
-      <c r="Y17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI17" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AJ17" t="n">
         <v>1.08</v>
@@ -3870,16 +3870,16 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF17" t="n">
         <v>1.14</v>
@@ -3962,13 +3962,13 @@
         <v>4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="T18" t="n">
         <v>1.82</v>
       </c>
       <c r="U18" t="n">
-        <v>5.45</v>
+        <v>5.55</v>
       </c>
       <c r="V18" t="n">
         <v>1.44</v>
@@ -3992,7 +3992,7 @@
         <v>1.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AD18" t="n">
         <v>2.74</v>
@@ -4001,7 +4001,7 @@
         <v>2.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG18" t="n">
         <v>4.2</v>
@@ -4010,67 +4010,67 @@
         <v>1.19</v>
       </c>
       <c r="AI18" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK18" t="n">
         <v>1.95</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.45</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AV18" t="n">
         <v>2.52</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="BB18" t="n">
         <v>1.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BD18" t="n">
         <v>3.28</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1204,10 +1204,10 @@
         <v>2.45</v>
       </c>
       <c r="S4" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="T4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U4" t="n">
         <v>3.12</v>
@@ -1219,55 +1219,55 @@
         <v>2.41</v>
       </c>
       <c r="X4" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>2.06</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1404,10 +1404,10 @@
         <v>1.73</v>
       </c>
       <c r="T5" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="U5" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="V5" t="n">
         <v>1.3</v>
@@ -1416,16 +1416,16 @@
         <v>3.16</v>
       </c>
       <c r="X5" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="Y5" t="n">
         <v>1.47</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB5" t="n">
         <v>1</v>
@@ -1434,19 +1434,19 @@
         <v>1.17</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AI5" t="n">
         <v>4.75</v>
@@ -1461,10 +1461,10 @@
         <v>1.72</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1473,28 +1473,28 @@
         <v>1.24</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AR5" t="n">
         <v>1.82</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.37</v>
+        <v>3.34</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AW5" t="n">
         <v>1.86</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AY5" t="n">
         <v>1.28</v>
@@ -1506,19 +1506,19 @@
         <v>5.95</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BC5" t="n">
         <v>1.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="BE5" t="n">
         <v>1.83</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1598,7 +1598,7 @@
         <v>3.83</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T6" t="n">
         <v>2.1</v>
@@ -1607,10 +1607,10 @@
         <v>4.61</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="X6" t="n">
         <v>2.63</v>
@@ -1706,13 +1706,13 @@
         <v>1.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="BD6" t="n">
         <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="BF6" t="n">
         <v>1.18</v>
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S8" t="n">
         <v>3.8</v>
@@ -1998,13 +1998,13 @@
         <v>1.97</v>
       </c>
       <c r="U8" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="X8" t="n">
         <v>3.05</v>
@@ -2013,19 +2013,19 @@
         <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC8" t="n">
         <v>1.36</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="AE8" t="n">
         <v>2.14</v>
@@ -2034,7 +2034,7 @@
         <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AH8" t="n">
         <v>1.25</v>
@@ -2049,10 +2049,10 @@
         <v>1.85</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AN8" t="n">
         <v>1.3</v>
@@ -2061,25 +2061,25 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.54</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AW8" t="n">
         <v>1.8</v>
@@ -2088,25 +2088,25 @@
         <v>1.47</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="BB8" t="n">
         <v>1.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="BD8" t="n">
         <v>3.25</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BF8" t="n">
         <v>1.13</v>
@@ -2183,13 +2183,13 @@
         <v>3.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R9" t="n">
         <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>4.72</v>
+        <v>5.05</v>
       </c>
       <c r="T9" t="n">
         <v>1.8</v>
@@ -2201,13 +2201,13 @@
         <v>1.78</v>
       </c>
       <c r="W9" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="X9" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
         <v>15</v>
@@ -2219,19 +2219,19 @@
         <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="AH9" t="n">
         <v>1.06</v>
@@ -2240,10 +2240,10 @@
         <v>14</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AL9" t="n">
         <v>1.5</v>
@@ -2261,13 +2261,13 @@
         <v>1.51</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AR9" t="n">
         <v>2.55</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="AT9" t="n">
         <v>5.12</v>
@@ -2276,13 +2276,13 @@
         <v>2.35</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AW9" t="n">
         <v>1.46</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AY9" t="n">
         <v>1.08</v>
@@ -2294,16 +2294,16 @@
         <v>1.92</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BF9" t="n">
         <v>1.05</v>
@@ -2386,7 +2386,7 @@
         <v>8.4</v>
       </c>
       <c r="S10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="T10" t="n">
         <v>2.3</v>
@@ -2419,37 +2419,37 @@
         <v>1.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
         <v>4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK10" t="n">
         <v>2.1</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
         <v>1.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="BD10" t="n">
         <v>3.5</v>
@@ -2503,7 +2503,7 @@
         <v>1.62</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2616,13 +2616,13 @@
         <v>1.43</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AE11" t="n">
         <v>2.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
         <v>4.25</v>
@@ -2643,7 +2643,7 @@
         <v>1.6</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="AN11" t="n">
         <v>1.2</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="AF12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR12" t="n">
         <v>2.15</v>
       </c>
-      <c r="U12" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U13" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.31</v>
       </c>
-      <c r="Q13" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V13" t="n">
+      <c r="Z13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.22</v>
       </c>
-      <c r="W13" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI13" t="n">
-        <v>3.62</v>
+        <v>7.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AN13" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S9" t="n">
         <v>5.05</v>
@@ -2198,10 +2198,10 @@
         <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="W9" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="X9" t="n">
         <v>4.45</v>
@@ -2222,7 +2222,7 @@
         <v>1.82</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AE9" t="n">
         <v>3.3</v>
@@ -2231,7 +2231,7 @@
         <v>1.29</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="AH9" t="n">
         <v>1.06</v>
@@ -2261,10 +2261,10 @@
         <v>1.51</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AS9" t="n">
         <v>3.42</v>
@@ -2276,7 +2276,7 @@
         <v>2.35</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AW9" t="n">
         <v>1.46</v>
@@ -2288,16 +2288,16 @@
         <v>1.08</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="BA9" t="n">
         <v>1.92</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BD9" t="n">
         <v>2.3</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.9</v>
+        <v>4.55</v>
       </c>
       <c r="R10" t="n">
-        <v>8.4</v>
+        <v>6.7</v>
       </c>
       <c r="S10" t="n">
         <v>1.75</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>2.97</v>
+        <v>3.7</v>
       </c>
       <c r="X10" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE10" t="n">
+      <c r="AQ10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AW10" t="n">
         <v>1.87</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AX10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.91</v>
       </c>
-      <c r="AG10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
+      <c r="BF10" t="n">
         <v>1.25</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.55</v>
+        <v>4.9</v>
       </c>
       <c r="R12" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
       <c r="S12" t="n">
         <v>1.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>3.7</v>
+        <v>2.97</v>
       </c>
       <c r="X12" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.05</v>
+        <v>3.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.35</v>
+        <v>2.97</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="AM12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BF12" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3168,25 +3168,25 @@
         <v>2.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="R14" t="n">
         <v>2.75</v>
       </c>
       <c r="S14" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="U14" t="n">
         <v>3.5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W14" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X14" t="n">
         <v>3.5</v>
@@ -3201,13 +3201,13 @@
         <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AE14" t="n">
         <v>2.5</v>
@@ -3216,7 +3216,7 @@
         <v>1.44</v>
       </c>
       <c r="AG14" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="AH14" t="n">
         <v>1.14</v>
@@ -3225,13 +3225,13 @@
         <v>10.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AK14" t="n">
         <v>2.05</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AM14" t="n">
         <v>1.4</v>
@@ -3371,19 +3371,19 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="T15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U15" t="n">
         <v>4.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="X15" t="n">
         <v>3.75</v>
@@ -3407,13 +3407,13 @@
         <v>2.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="AF15" t="n">
         <v>1.33</v>
       </c>
       <c r="AG15" t="n">
-        <v>6</v>
+        <v>5.94</v>
       </c>
       <c r="AH15" t="n">
         <v>1.12</v>
@@ -3428,13 +3428,13 @@
         <v>2.25</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AM15" t="n">
         <v>1.38</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3443,10 +3443,10 @@
         <v>1.24</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AS15" t="n">
         <v>2.38</v>
@@ -3455,10 +3455,10 @@
         <v>3.21</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AW15" t="n">
         <v>1.83</v>
@@ -3470,10 +3470,10 @@
         <v>1.26</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.31</v>
+        <v>2.4</v>
       </c>
       <c r="BB15" t="n">
         <v>1.39</v>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q17" t="n">
         <v>3.25</v>
@@ -3765,25 +3765,25 @@
         <v>4.83</v>
       </c>
       <c r="S17" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U17" t="n">
-        <v>4.6</v>
+        <v>5.46</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="W17" t="n">
-        <v>2.71</v>
+        <v>2.31</v>
       </c>
       <c r="X17" t="n">
         <v>2.94</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z17" t="n">
         <v>7.2</v>
@@ -3795,10 +3795,10 @@
         <v>1.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3813,7 +3813,7 @@
         <v>1.24</v>
       </c>
       <c r="AI17" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="AJ17" t="n">
         <v>1.08</v>
@@ -3870,10 +3870,10 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="BD17" t="n">
         <v>3.34</v>
@@ -3953,31 +3953,31 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q18" t="n">
         <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="S18" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="T18" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="U18" t="n">
-        <v>5.55</v>
+        <v>5.45</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="Y18" t="n">
         <v>1.28</v>
@@ -3989,7 +3989,7 @@
         <v>1.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC18" t="n">
         <v>1.37</v>
@@ -3998,13 +3998,13 @@
         <v>2.74</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AF18" t="n">
         <v>1.63</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AH18" t="n">
         <v>1.19</v>
@@ -4013,34 +4013,34 @@
         <v>8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.45</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AT18" t="n">
         <v>2.7</v>
@@ -4049,19 +4049,19 @@
         <v>3.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="AW18" t="n">
         <v>1.92</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AY18" t="n">
         <v>1.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BA18" t="n">
         <v>3.74</v>
@@ -4070,7 +4070,7 @@
         <v>1.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="BD18" t="n">
         <v>3.28</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1204,10 +1204,10 @@
         <v>2.45</v>
       </c>
       <c r="S4" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="T4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U4" t="n">
         <v>3.12</v>
@@ -1219,61 +1219,61 @@
         <v>2.41</v>
       </c>
       <c r="X4" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN4" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.79</v>
@@ -1282,7 +1282,7 @@
         <v>2.78</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AT4" t="n">
         <v>4.52</v>
@@ -1294,10 +1294,10 @@
         <v>1.92</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AY4" t="n">
         <v>1.12</v>
@@ -1309,19 +1309,19 @@
         <v>2.06</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Q5" t="n">
         <v>4.72</v>
@@ -1401,31 +1401,31 @@
         <v>8.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="T5" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="U5" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="X5" t="n">
         <v>2.56</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB5" t="n">
         <v>1</v>
@@ -1446,7 +1446,7 @@
         <v>2.77</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AI5" t="n">
         <v>4.75</v>
@@ -1461,10 +1461,10 @@
         <v>1.72</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1473,28 +1473,28 @@
         <v>1.24</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AR5" t="n">
         <v>1.82</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AW5" t="n">
         <v>1.86</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AY5" t="n">
         <v>1.28</v>
@@ -1506,19 +1506,19 @@
         <v>5.95</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BC5" t="n">
         <v>1.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="BE5" t="n">
         <v>1.83</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.55</v>
+        <v>4.9</v>
       </c>
       <c r="R10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
       <c r="S10" t="n">
         <v>1.75</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>3.7</v>
+        <v>2.97</v>
       </c>
       <c r="X10" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>5.05</v>
+        <v>3.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.35</v>
+        <v>2.97</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="AM10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BF10" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.91</v>
+        <v>3.85</v>
       </c>
       <c r="R11" t="n">
-        <v>1.85</v>
+        <v>6.2</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
-        <v>2.54</v>
+        <v>7.34</v>
       </c>
       <c r="V11" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>2.22</v>
+        <v>2.53</v>
       </c>
       <c r="X11" t="n">
-        <v>3.34</v>
+        <v>2.97</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC11" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.46</v>
+        <v>2.97</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.4</v>
+        <v>1.68</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AI11" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.9</v>
+        <v>4.55</v>
       </c>
       <c r="R12" t="n">
-        <v>8.4</v>
+        <v>6.7</v>
       </c>
       <c r="S12" t="n">
         <v>1.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="U12" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="W12" t="n">
-        <v>2.97</v>
+        <v>3.7</v>
       </c>
       <c r="X12" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE12" t="n">
+      <c r="AQ12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AW12" t="n">
         <v>1.87</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AX12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.91</v>
       </c>
-      <c r="AG12" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
+      <c r="BF12" t="n">
         <v>1.25</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.85</v>
+        <v>2.91</v>
       </c>
       <c r="R13" t="n">
-        <v>6.2</v>
+        <v>1.85</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="U13" t="n">
-        <v>7.34</v>
+        <v>2.54</v>
       </c>
       <c r="V13" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="W13" t="n">
-        <v>2.53</v>
+        <v>2.22</v>
       </c>
       <c r="X13" t="n">
-        <v>2.97</v>
+        <v>3.34</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM13" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AN13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.33</v>
       </c>
-      <c r="AD13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BC13" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="S4" t="n">
         <v>3.66</v>
@@ -1216,7 +1216,7 @@
         <v>1.49</v>
       </c>
       <c r="W4" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="X4" t="n">
         <v>3.35</v>
@@ -1234,7 +1234,7 @@
         <v>1.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AD4" t="n">
         <v>2.52</v>
@@ -1249,7 +1249,7 @@
         <v>4.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AI4" t="n">
         <v>8.300000000000001</v>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Q5" t="n">
         <v>4.72</v>
       </c>
       <c r="R5" t="n">
-        <v>8.25</v>
+        <v>11.5</v>
       </c>
       <c r="S5" t="n">
         <v>1.78</v>
@@ -1416,10 +1416,10 @@
         <v>3.15</v>
       </c>
       <c r="X5" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z5" t="n">
         <v>5.7</v>
@@ -1473,37 +1473,37 @@
         <v>1.24</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.95</v>
+        <v>5.05</v>
       </c>
       <c r="BB5" t="n">
         <v>1.15</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>3.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R8" t="n">
-        <v>3.83</v>
+        <v>1.9</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R9" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
         <v>5.05</v>
@@ -2195,13 +2195,13 @@
         <v>1.8</v>
       </c>
       <c r="U9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="W9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="X9" t="n">
         <v>4.45</v>
@@ -2219,22 +2219,22 @@
         <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AG9" t="n">
-        <v>8</v>
+        <v>6.75</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AI9" t="n">
         <v>14</v>
@@ -2264,7 +2264,7 @@
         <v>1.89</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.46</v>
+        <v>3.08</v>
       </c>
       <c r="AS9" t="n">
         <v>3.42</v>
@@ -2291,13 +2291,13 @@
         <v>2.25</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BD9" t="n">
         <v>2.3</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.29</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.9</v>
+        <v>2.91</v>
       </c>
       <c r="R10" t="n">
-        <v>8.4</v>
+        <v>1.85</v>
       </c>
       <c r="S10" t="n">
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>8</v>
+        <v>2.54</v>
       </c>
       <c r="V10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM10" t="n">
         <v>1.31</v>
       </c>
-      <c r="W10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="AN10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC10" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="R13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>8</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI13" t="n">
         <v>4</v>
       </c>
-      <c r="Q13" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="S13" t="n">
-        <v>6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AH13" t="n">
+      <c r="AJ13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.08</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="R14" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="S14" t="n">
         <v>3.34</v>
@@ -3201,10 +3201,10 @@
         <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AD14" t="n">
         <v>2.4</v>
@@ -3216,7 +3216,7 @@
         <v>1.44</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="AH14" t="n">
         <v>1.14</v>
@@ -3231,13 +3231,13 @@
         <v>2.05</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BC14" t="n">
         <v>2.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BE14" t="n">
         <v>1.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3392,7 +3392,7 @@
         <v>1.16</v>
       </c>
       <c r="Z15" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AA15" t="n">
         <v>1.03</v>
@@ -3401,7 +3401,7 @@
         <v>1.08</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AD15" t="n">
         <v>2.22</v>
@@ -3425,13 +3425,13 @@
         <v>1.03</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AL15" t="n">
         <v>1.53</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AN15" t="n">
         <v>1.59</v>
@@ -3440,40 +3440,40 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AQ15" t="n">
         <v>1.47</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="AV15" t="n">
         <v>2.35</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AY15" t="n">
         <v>1.26</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="BB15" t="n">
         <v>1.39</v>
@@ -3759,19 +3759,19 @@
         <v>1.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>4.83</v>
+        <v>4.35</v>
       </c>
       <c r="S17" t="n">
         <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>5.46</v>
+        <v>4.6</v>
       </c>
       <c r="V17" t="n">
         <v>1.51</v>
@@ -3780,10 +3780,10 @@
         <v>2.31</v>
       </c>
       <c r="X17" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z17" t="n">
         <v>7.2</v>
@@ -3792,22 +3792,22 @@
         <v>1.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AD17" t="n">
         <v>3.15</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AH17" t="n">
         <v>1.24</v>
@@ -3873,10 +3873,10 @@
         <v>1.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="BE17" t="n">
         <v>1.57</v>
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="S18" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="T18" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U18" t="n">
-        <v>5.45</v>
+        <v>5.9</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W18" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="X18" t="n">
-        <v>3.23</v>
+        <v>3.12</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AA18" t="n">
         <v>1.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AG18" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AI18" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4043,10 +4043,10 @@
         <v>2.25</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="AV18" t="n">
         <v>2.48</v>
@@ -4067,19 +4067,19 @@
         <v>3.74</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>3.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R6" t="n">
-        <v>3.83</v>
+        <v>1.9</v>
       </c>
       <c r="S6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.15</v>
       </c>
-      <c r="S7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.97</v>
-      </c>
       <c r="U7" t="n">
-        <v>2.7</v>
+        <v>4.61</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>2.53</v>
+        <v>2.83</v>
       </c>
       <c r="X7" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.9</v>
+        <v>3.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.7</v>
+        <v>2.92</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL8" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2380,16 +2380,16 @@
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="R10" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>5.34</v>
       </c>
       <c r="T10" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
         <v>2.54</v>
@@ -2416,37 +2416,37 @@
         <v>1.08</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="AE10" t="n">
         <v>2.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AH10" t="n">
         <v>1.17</v>
       </c>
       <c r="AI10" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ10" t="n">
         <v>1.05</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AN10" t="n">
         <v>1.2</v>
@@ -2494,7 +2494,7 @@
         <v>1.33</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BD10" t="n">
         <v>2.9</v>
@@ -2503,7 +2503,7 @@
         <v>1.44</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.85</v>
+        <v>4.85</v>
       </c>
       <c r="R11" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T11" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>7.34</v>
+        <v>8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>2.53</v>
+        <v>2.97</v>
       </c>
       <c r="X11" t="n">
-        <v>2.97</v>
+        <v>2.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>6.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB11" t="n">
         <v>1.01</v>
       </c>
       <c r="AC11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.33</v>
       </c>
-      <c r="AD11" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AI11" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.62</v>
       </c>
-      <c r="AM11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.55</v>
+        <v>3.75</v>
       </c>
       <c r="R12" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="U12" t="n">
-        <v>6.5</v>
+        <v>6.74</v>
       </c>
       <c r="V12" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>3.7</v>
+        <v>2.53</v>
       </c>
       <c r="X12" t="n">
-        <v>2.18</v>
+        <v>3.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.9</v>
+        <v>8.1</v>
       </c>
       <c r="AA12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF12" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="R13" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="S13" t="n">
         <v>1.75</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="U13" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>2.97</v>
+        <v>3.66</v>
       </c>
       <c r="X13" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.1</v>
+        <v>4.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF13" t="n">
+      <c r="AQ13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.91</v>
       </c>
-      <c r="AG13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
+      <c r="BF13" t="n">
         <v>1.25</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="S4" t="n">
         <v>3.66</v>
@@ -1216,7 +1216,7 @@
         <v>1.49</v>
       </c>
       <c r="W4" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="X4" t="n">
         <v>3.35</v>
@@ -1240,10 +1240,10 @@
         <v>2.52</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG4" t="n">
         <v>4.25</v>
@@ -1264,43 +1264,43 @@
         <v>1.75</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.78</v>
+        <v>2.25</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.52</v>
+        <v>4.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AZ4" t="n">
         <v>2.17</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.72</v>
+        <v>4.8</v>
       </c>
       <c r="R5" t="n">
         <v>11.5</v>
@@ -1410,10 +1410,10 @@
         <v>7.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="X5" t="n">
         <v>2.47</v>
@@ -1443,7 +1443,7 @@
         <v>2.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="AH5" t="n">
         <v>1.38</v>
@@ -1473,25 +1473,25 @@
         <v>1.24</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.84</v>
+        <v>2.09</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AX5" t="n">
         <v>1.51</v>
@@ -1500,10 +1500,10 @@
         <v>1.27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.05</v>
+        <v>4.7</v>
       </c>
       <c r="BB5" t="n">
         <v>1.15</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.44</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9</v>
+        <v>3.83</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>3.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R7" t="n">
-        <v>3.83</v>
+        <v>1.9</v>
       </c>
       <c r="S7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="R11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="S11" t="n">
         <v>1.75</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>2.97</v>
+        <v>3.66</v>
       </c>
       <c r="X11" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.15</v>
+        <v>4.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF11" t="n">
+      <c r="AQ11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.91</v>
       </c>
-      <c r="AG11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
+      <c r="BF11" t="n">
         <v>1.25</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.75</v>
+        <v>4.85</v>
       </c>
       <c r="R12" t="n">
-        <v>6.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>6.74</v>
+        <v>8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>2.53</v>
+        <v>2.97</v>
       </c>
       <c r="X12" t="n">
-        <v>3.06</v>
+        <v>2.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.1</v>
+        <v>6.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.33</v>
       </c>
-      <c r="AD12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE12" t="n">
+      <c r="AI12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK12" t="n">
         <v>2.1</v>
       </c>
-      <c r="AF12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AL12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.62</v>
       </c>
-      <c r="AM12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BF12" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.95</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="T13" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="U13" t="n">
-        <v>6.5</v>
+        <v>6.74</v>
       </c>
       <c r="V13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.22</v>
       </c>
-      <c r="W13" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI13" t="n">
-        <v>3.95</v>
+        <v>7.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.5</v>
       </c>
-      <c r="AY13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1198,13 +1198,13 @@
         <v>2.47</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="R4" t="n">
-        <v>2.45</v>
+        <v>3.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3.66</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
         <v>1.93</v>
@@ -1213,7 +1213,7 @@
         <v>3.12</v>
       </c>
       <c r="V4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
         <v>2.39</v>
@@ -1246,7 +1246,7 @@
         <v>1.58</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AH4" t="n">
         <v>1.15</v>
@@ -1264,31 +1264,31 @@
         <v>1.75</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.77</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AT4" t="n">
         <v>4.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AV4" t="n">
         <v>1.94</v>
@@ -1297,7 +1297,7 @@
         <v>1.56</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AY4" t="n">
         <v>1.13</v>
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.8</v>
+        <v>4.72</v>
       </c>
       <c r="R5" t="n">
-        <v>11.5</v>
+        <v>8.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="T5" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="U5" t="n">
-        <v>7.4</v>
+        <v>8.06</v>
       </c>
       <c r="V5" t="n">
         <v>1.3</v>
@@ -1428,7 +1428,7 @@
         <v>1.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
         <v>1.17</v>
@@ -1437,10 +1437,10 @@
         <v>3.94</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AG5" t="n">
         <v>2.62</v>
@@ -1473,13 +1473,13 @@
         <v>1.24</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AR5" t="n">
         <v>2.09</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="AT5" t="n">
         <v>3.14</v>
@@ -1488,13 +1488,13 @@
         <v>3.34</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AY5" t="n">
         <v>1.27</v>
@@ -1604,7 +1604,7 @@
         <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>4.61</v>
+        <v>4.65</v>
       </c>
       <c r="V6" t="n">
         <v>1.34</v>
@@ -1613,7 +1613,7 @@
         <v>2.83</v>
       </c>
       <c r="X6" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="Y6" t="n">
         <v>1.39</v>
@@ -1628,22 +1628,22 @@
         <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
         <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" t="n">
         <v>5.7</v>
@@ -1652,10 +1652,10 @@
         <v>1.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AM6" t="n">
         <v>1.22</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL7" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="R8" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="S8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1001,76 +1001,76 @@
         <v>1.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="R3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>3.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R6" t="n">
-        <v>3.83</v>
+        <v>1.9</v>
       </c>
       <c r="S6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>2.09</v>
+        <v>3.62</v>
       </c>
       <c r="S7" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
         <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>2.75</v>
+        <v>4.45</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>2.53</v>
+        <v>2.83</v>
       </c>
       <c r="X7" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.9</v>
+        <v>6.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.9</v>
+        <v>3.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AH7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM7" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AN7" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.92</v>
+        <v>7.5</v>
       </c>
       <c r="S10" t="n">
-        <v>5.34</v>
+        <v>1.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>2.54</v>
+        <v>8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>2.22</v>
+        <v>2.97</v>
       </c>
       <c r="X10" t="n">
-        <v>3.34</v>
+        <v>2.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.5</v>
+        <v>6.15</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC10" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.64</v>
+        <v>3.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>8.300000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AK10" t="n">
         <v>2.1</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.36</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.95</v>
+        <v>2.92</v>
       </c>
       <c r="R11" t="n">
-        <v>7.1</v>
+        <v>1.83</v>
       </c>
       <c r="S11" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.63</v>
+        <v>1.82</v>
       </c>
       <c r="U11" t="n">
-        <v>6.5</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="W11" t="n">
-        <v>3.66</v>
+        <v>2.22</v>
       </c>
       <c r="X11" t="n">
-        <v>2.2</v>
+        <v>3.34</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BA11" t="n">
         <v>1.63</v>
       </c>
-      <c r="Z11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.75</v>
-      </c>
       <c r="BB11" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.85</v>
+        <v>3.55</v>
       </c>
       <c r="R12" t="n">
-        <v>8.199999999999999</v>
+        <v>5.75</v>
       </c>
       <c r="S12" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="T12" t="n">
         <v>2.3</v>
       </c>
       <c r="U12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z12" t="n">
         <v>8</v>
       </c>
-      <c r="V12" t="n">
+      <c r="AA12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.31</v>
       </c>
-      <c r="W12" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="X12" t="n">
+      <c r="AD12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR12" t="n">
         <v>2.6</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM12" t="n">
+      <c r="AS12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY12" t="n">
         <v>1.15</v>
       </c>
-      <c r="AN12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U13" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH13" t="n">
+      <c r="AR13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM13" t="n">
+      <c r="BA13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.13</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="Q4" t="n">
         <v>2.83</v>
       </c>
       <c r="R4" t="n">
-        <v>3.38</v>
+        <v>2.5</v>
       </c>
       <c r="S4" t="n">
         <v>3.45</v>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.72</v>
+        <v>4.55</v>
       </c>
       <c r="R5" t="n">
-        <v>8.25</v>
+        <v>7.6</v>
       </c>
       <c r="S5" t="n">
         <v>1.75</v>
@@ -1428,25 +1428,25 @@
         <v>1.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.94</v>
+        <v>4.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AI5" t="n">
         <v>4.75</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,80 +1786,80 @@
         </is>
       </c>
       <c r="P7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="AL7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN7" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>2.18</v>
+        <v>3.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>2.53</v>
+        <v>2.83</v>
       </c>
       <c r="X8" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.75</v>
+        <v>6.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.04</v>
+        <v>3.48</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.8</v>
+        <v>2.92</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AI8" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2180,37 +2180,37 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="U9" t="n">
         <v>3.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="W9" t="n">
         <v>1.92</v>
       </c>
       <c r="X9" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="Y9" t="n">
         <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA9" t="n">
         <v>1.03</v>
@@ -2219,34 +2219,34 @@
         <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="AH9" t="n">
         <v>1.04</v>
       </c>
       <c r="AI9" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.01</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AM9" t="n">
         <v>1.44</v>
@@ -2258,46 +2258,46 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.08</v>
+        <v>2.42</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.42</v>
+        <v>3.21</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.12</v>
+        <v>4.73</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BD9" t="n">
         <v>2.3</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.92</v>
+        <v>3.55</v>
       </c>
       <c r="R11" t="n">
-        <v>1.83</v>
+        <v>5.75</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1.94</v>
       </c>
       <c r="T11" t="n">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>2.22</v>
+        <v>2.47</v>
       </c>
       <c r="X11" t="n">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.46</v>
+        <v>2.83</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AI11" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL11" t="n">
         <v>1.62</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.82</v>
+        <v>2.9</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.89</v>
+        <v>4.15</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.17</v>
+        <v>2.66</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.62</v>
+        <v>1.24</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.63</v>
+        <v>4.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R12" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="AR12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.24</v>
-      </c>
       <c r="BA12" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW13" t="n">
         <v>1.38</v>
       </c>
-      <c r="Q13" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="AX13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>2.62</v>
       </c>
-      <c r="U13" t="n">
-        <v>6</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Y13" t="n">
+      <c r="BA13" t="n">
         <v>1.63</v>
       </c>
-      <c r="Z13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE13" t="n">
+      <c r="BB13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.44</v>
       </c>
-      <c r="AF13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.07</v>
-      </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,16 +3165,16 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="R14" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="S14" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="T14" t="n">
         <v>1.95</v>
@@ -3186,7 +3186,7 @@
         <v>1.57</v>
       </c>
       <c r="W14" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="X14" t="n">
         <v>3.5</v>
@@ -3195,22 +3195,22 @@
         <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA14" t="n">
         <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AF14" t="n">
         <v>1.44</v>
@@ -3219,7 +3219,7 @@
         <v>4.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AI14" t="n">
         <v>10.5</v>
@@ -3234,10 +3234,10 @@
         <v>1.67</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3362,61 +3362,61 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="S15" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="T15" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="U15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W15" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="X15" t="n">
         <v>3.75</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AA15" t="n">
         <v>1.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>5.94</v>
+        <v>5.93</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AI15" t="n">
         <v>11</v>
@@ -3425,16 +3425,16 @@
         <v>1.03</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3443,46 +3443,46 @@
         <v>1.25</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="AV15" t="n">
         <v>2.35</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AY15" t="n">
         <v>1.26</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.51</v>
+        <v>2.18</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="BE15" t="n">
         <v>1.33</v>
@@ -3756,31 +3756,31 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R17" t="n">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="U17" t="n">
-        <v>4.6</v>
+        <v>5.46</v>
       </c>
       <c r="V17" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="W17" t="n">
-        <v>2.31</v>
+        <v>2.71</v>
       </c>
       <c r="X17" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="Y17" t="n">
         <v>1.32</v>
@@ -3792,25 +3792,25 @@
         <v>1.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AF17" t="n">
         <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" t="n">
         <v>5.75</v>
@@ -3873,7 +3873,7 @@
         <v>1.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BD17" t="n">
         <v>3.3</v>
@@ -3953,43 +3953,43 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="S18" t="n">
-        <v>2.41</v>
+        <v>2.17</v>
       </c>
       <c r="T18" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="U18" t="n">
-        <v>5.9</v>
+        <v>6.05</v>
       </c>
       <c r="V18" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="X18" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
         <v>1.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
         <v>1.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
         <v>1.33</v>
@@ -3998,46 +3998,46 @@
         <v>2.83</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="AH18" t="n">
         <v>1.21</v>
       </c>
       <c r="AI18" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="AJ18" t="n">
         <v>1.03</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AL18" t="n">
         <v>1.73</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.45</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="AS18" t="n">
         <v>2.25</v>
@@ -4058,10 +4058,10 @@
         <v>1.56</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="BA18" t="n">
         <v>3.74</v>
@@ -4070,13 +4070,13 @@
         <v>1.24</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="BD18" t="n">
         <v>3.34</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BF18" t="n">
         <v>1.11</v>
@@ -4356,70 +4356,70 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1198,10 +1198,10 @@
         <v>2.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="S4" t="n">
         <v>3.45</v>
@@ -1210,7 +1210,7 @@
         <v>1.93</v>
       </c>
       <c r="U4" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="V4" t="n">
         <v>1.5</v>
@@ -1264,10 +1264,10 @@
         <v>1.75</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AR4" t="n">
         <v>2.73</v>
@@ -1291,7 +1291,7 @@
         <v>2.55</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AW4" t="n">
         <v>1.56</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q5" t="n">
         <v>4.55</v>
@@ -1401,13 +1401,13 @@
         <v>7.6</v>
       </c>
       <c r="S5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="T5" t="n">
         <v>2.34</v>
       </c>
       <c r="U5" t="n">
-        <v>8.06</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>1.3</v>
@@ -1416,7 +1416,7 @@
         <v>3.16</v>
       </c>
       <c r="X5" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="Y5" t="n">
         <v>1.47</v>
@@ -1458,7 +1458,7 @@
         <v>2.01</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AM5" t="n">
         <v>1.17</v>
@@ -1473,19 +1473,19 @@
         <v>1.24</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AR5" t="n">
         <v>2.09</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="AT5" t="n">
         <v>3.14</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AV5" t="n">
         <v>2.37</v>
@@ -1494,7 +1494,7 @@
         <v>1.84</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AY5" t="n">
         <v>1.27</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,130 +1589,130 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="S6" t="n">
-        <v>3.7</v>
+        <v>4.03</v>
       </c>
       <c r="T6" t="n">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="U6" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>2.53</v>
+        <v>2.78</v>
       </c>
       <c r="X6" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
         <v>6.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.04</v>
+        <v>3.29</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="AH6" t="n">
         <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.23</v>
+        <v>1.74</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.41</v>
+        <v>2.48</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.1</v>
+        <v>4.39</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AX6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY6" t="n">
         <v>1.45</v>
       </c>
-      <c r="AY6" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="BF6" t="n">
         <v>1.13</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>2.03</v>
+        <v>4.48</v>
       </c>
       <c r="S7" t="n">
-        <v>4.37</v>
+        <v>2.29</v>
       </c>
       <c r="T7" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>2.59</v>
+        <v>4.85</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="X7" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.18</v>
+        <v>3.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF7" t="n">
         <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.3</v>
+        <v>1.93</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AL8" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.81</v>
+        <v>1.24</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2204,19 +2204,19 @@
         <v>1.92</v>
       </c>
       <c r="X9" t="n">
-        <v>4.33</v>
+        <v>3.95</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
         <v>1.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AC9" t="n">
         <v>1.78</v>
@@ -2225,7 +2225,7 @@
         <v>1.93</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AF9" t="n">
         <v>1.28</v>
@@ -2234,7 +2234,7 @@
         <v>6.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AI9" t="n">
         <v>21</v>
@@ -2261,7 +2261,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR9" t="n">
         <v>2.42</v>
@@ -2273,10 +2273,10 @@
         <v>4.73</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AW9" t="n">
         <v>1.49</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.6</v>
+        <v>2.92</v>
       </c>
       <c r="R10" t="n">
-        <v>7.5</v>
+        <v>1.83</v>
       </c>
       <c r="S10" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>8</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
-        <v>2.97</v>
+        <v>2.22</v>
       </c>
       <c r="X10" t="n">
-        <v>2.6</v>
+        <v>3.34</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.15</v>
+        <v>10</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.4</v>
+        <v>2.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AK10" t="n">
         <v>2.1</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.44</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.67</v>
-      </c>
       <c r="BF10" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="R12" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="S12" t="n">
         <v>1.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>3.66</v>
+        <v>2.97</v>
       </c>
       <c r="X12" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.75</v>
+        <v>6.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM12" t="n">
         <v>1.15</v>
       </c>
-      <c r="AD12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE12" t="n">
+      <c r="AN12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
         <v>1.44</v>
       </c>
-      <c r="AF12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM12" t="n">
+      <c r="AQ12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF12" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>1.37</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.92</v>
+        <v>4.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.83</v>
+        <v>6.5</v>
       </c>
       <c r="S13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD13" t="n">
         <v>5</v>
       </c>
-      <c r="T13" t="n">
+      <c r="AE13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.82</v>
       </c>
-      <c r="U13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AL13" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.68</v>
+        <v>2.12</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.82</v>
+        <v>2.32</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.89</v>
+        <v>2.75</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.17</v>
+        <v>3.23</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.7</v>
+        <v>2.39</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.38</v>
+        <v>1.92</v>
       </c>
       <c r="AX13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.18</v>
       </c>
-      <c r="AY13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BC13" t="n">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3365,7 +3365,7 @@
         <v>1.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="R15" t="n">
         <v>3.92</v>
@@ -3404,7 +3404,7 @@
         <v>1.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AE15" t="n">
         <v>2.81</v>
@@ -3431,10 +3431,10 @@
         <v>1.5</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3449,7 +3449,7 @@
         <v>1.86</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AT15" t="n">
         <v>3.2</v>
@@ -3461,10 +3461,10 @@
         <v>2.35</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AY15" t="n">
         <v>1.26</v>
@@ -3476,7 +3476,7 @@
         <v>2.18</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BC15" t="n">
         <v>2.9</v>
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R18" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="S18" t="n">
         <v>2.17</v>
@@ -3968,34 +3968,34 @@
         <v>2.11</v>
       </c>
       <c r="U18" t="n">
-        <v>6.05</v>
+        <v>6.1</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
         <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="AE18" t="n">
         <v>2.12</v>
@@ -4004,16 +4004,16 @@
         <v>1.7</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AI18" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK18" t="n">
         <v>1.95</v>
@@ -4022,10 +4022,10 @@
         <v>1.73</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>3.74</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BC18" t="n">
         <v>2.33</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AD20" t="n">
         <v>4.6</v>
@@ -4410,10 +4410,10 @@
         <v>1.21</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="AM20" t="n">
         <v>1.2</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,112 +1589,112 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.78</v>
+        <v>1.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
-        <v>2.23</v>
+        <v>4.48</v>
       </c>
       <c r="S6" t="n">
-        <v>4.03</v>
+        <v>2.29</v>
       </c>
       <c r="T6" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>2.58</v>
+        <v>4.85</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="X6" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.75</v>
+        <v>6.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.29</v>
+        <v>3.48</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.25</v>
+        <v>5.7</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AL6" t="n">
         <v>1.92</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.17</v>
+        <v>1.99</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>4.48</v>
+        <v>2.18</v>
       </c>
       <c r="S7" t="n">
-        <v>2.29</v>
+        <v>3.7</v>
       </c>
       <c r="T7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE7" t="n">
         <v>2.1</v>
       </c>
-      <c r="U7" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.92</v>
+        <v>3.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.93</v>
+        <v>1.24</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,130 +1983,130 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="S8" t="n">
-        <v>3.7</v>
+        <v>4.03</v>
       </c>
       <c r="T8" t="n">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="U8" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>2.53</v>
+        <v>2.78</v>
       </c>
       <c r="X8" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
         <v>6.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.04</v>
+        <v>3.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="AH8" t="n">
         <v>1.25</v>
       </c>
       <c r="AI8" t="n">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.23</v>
+        <v>1.74</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.41</v>
+        <v>2.48</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.1</v>
+        <v>4.39</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AX8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY8" t="n">
         <v>1.45</v>
       </c>
-      <c r="AY8" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="BF8" t="n">
         <v>1.13</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,130 +2377,130 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="Q10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD10" t="n">
         <v>2.92</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AE10" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AI10" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AL10" t="n">
         <v>1.62</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.68</v>
+        <v>2.17</v>
       </c>
       <c r="AS10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT10" t="n">
         <v>3.82</v>
       </c>
-      <c r="AT10" t="n">
-        <v>5.89</v>
-      </c>
       <c r="AU10" t="n">
-        <v>2.17</v>
+        <v>2.66</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.62</v>
+        <v>1.24</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.63</v>
+        <v>4.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BF10" t="n">
         <v>1.1</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>6</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH11" t="n">
+      <c r="AR11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.24</v>
-      </c>
       <c r="BA11" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="R12" t="n">
         <v>7.5</v>
@@ -2789,7 +2789,7 @@
         <v>8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
         <v>2.97</v>
@@ -2798,7 +2798,7 @@
         <v>2.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z12" t="n">
         <v>6.15</v>
@@ -2807,25 +2807,25 @@
         <v>1.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC12" t="n">
         <v>1.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
         <v>3.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" t="n">
         <v>5.5</v>
@@ -2834,10 +2834,10 @@
         <v>1.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AM12" t="n">
         <v>1.15</v>
@@ -2849,40 +2849,40 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.4</v>
+        <v>4.38</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="BB12" t="n">
         <v>1.25</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.37</v>
+        <v>3.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.8</v>
+        <v>2.86</v>
       </c>
       <c r="R13" t="n">
-        <v>6.5</v>
+        <v>1.93</v>
       </c>
       <c r="S13" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>2.62</v>
       </c>
-      <c r="U13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE13" t="n">
+      <c r="BA13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.44</v>
       </c>
-      <c r="AF13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3174,7 +3174,7 @@
         <v>2.79</v>
       </c>
       <c r="S14" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="T14" t="n">
         <v>1.95</v>
@@ -3186,13 +3186,13 @@
         <v>1.57</v>
       </c>
       <c r="W14" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="X14" t="n">
         <v>3.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="n">
         <v>9.300000000000001</v>
@@ -3204,7 +3204,7 @@
         <v>1.07</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AD14" t="n">
         <v>2.3</v>
@@ -3243,34 +3243,34 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -3756,58 +3756,58 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="U17" t="n">
-        <v>5.46</v>
+        <v>5.95</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>2.71</v>
+        <v>2.36</v>
       </c>
       <c r="X17" t="n">
         <v>2.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AD17" t="n">
         <v>3.05</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AH17" t="n">
         <v>1.25</v>
@@ -3819,16 +3819,16 @@
         <v>1.08</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AM17" t="n">
         <v>1.3</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -4359,10 +4359,10 @@
         <v>2.8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="U20" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="V20" t="n">
         <v>1.2</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AD20" t="n">
         <v>4.6</v>
@@ -4410,10 +4410,10 @@
         <v>1.21</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="AM20" t="n">
         <v>1.2</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="Q4" t="n">
         <v>3.15</v>
@@ -1216,7 +1216,7 @@
         <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="X4" t="n">
         <v>3.35</v>
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="R5" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="S5" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="T5" t="n">
         <v>2.34</v>
       </c>
       <c r="U5" t="n">
-        <v>8.300000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="V5" t="n">
         <v>1.3</v>
@@ -1416,55 +1416,55 @@
         <v>3.16</v>
       </c>
       <c r="X5" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="AA5" t="n">
         <v>1.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
         <v>1.22</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.06</v>
+        <v>3.98</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AG5" t="n">
         <v>2.77</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1485,7 +1485,7 @@
         <v>3.14</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AV5" t="n">
         <v>2.37</v>
@@ -1509,13 +1509,13 @@
         <v>1.15</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BF5" t="n">
         <v>1.21</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>2.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>4.48</v>
+        <v>2.23</v>
       </c>
       <c r="S6" t="n">
-        <v>2.29</v>
+        <v>4.03</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="U6" t="n">
-        <v>4.85</v>
+        <v>2.58</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="X6" t="n">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.3</v>
+        <v>6.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.48</v>
+        <v>3.29</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.7</v>
+        <v>6.25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AL6" t="n">
         <v>1.92</v>
       </c>
       <c r="AM6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC6" t="n">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
         <v>3.8</v>
@@ -1843,7 +1843,7 @@
         <v>1.25</v>
       </c>
       <c r="AI7" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AJ7" t="n">
         <v>1.06</v>
@@ -1855,10 +1855,10 @@
         <v>1.83</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1891,7 +1891,7 @@
         <v>1.45</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AZ7" t="n">
         <v>2.6</v>
@@ -1906,13 +1906,13 @@
         <v>2.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,112 +1983,112 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.23</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>4.03</v>
+        <v>2.27</v>
       </c>
       <c r="T8" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="U8" t="n">
-        <v>2.58</v>
+        <v>4.9</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="X8" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.75</v>
+        <v>6.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AI8" t="n">
-        <v>6.25</v>
+        <v>5.7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.67</v>
+        <v>1.21</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.46</v>
+        <v>1.95</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -2100,16 +2100,16 @@
         <v>1.22</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.17</v>
+        <v>1.99</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2183,10 +2183,10 @@
         <v>3.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -2201,28 +2201,28 @@
         <v>1.77</v>
       </c>
       <c r="W9" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="X9" t="n">
-        <v>3.95</v>
+        <v>4.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA9" t="n">
         <v>1.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AE9" t="n">
         <v>3.28</v>
@@ -2231,7 +2231,7 @@
         <v>1.28</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="AH9" t="n">
         <v>1.06</v>
@@ -2243,10 +2243,10 @@
         <v>1.01</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AM9" t="n">
         <v>1.44</v>
@@ -2261,10 +2261,10 @@
         <v>1.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AS9" t="n">
         <v>3.21</v>
@@ -2276,7 +2276,7 @@
         <v>2.16</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AW9" t="n">
         <v>1.49</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="R10" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="T10" t="n">
         <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AX10" t="n">
         <v>1.4</v>
       </c>
-      <c r="W10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AY10" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.7</v>
+        <v>6.75</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="R11" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="S11" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>3.66</v>
+        <v>2.5</v>
       </c>
       <c r="X11" t="n">
-        <v>2.18</v>
+        <v>3.06</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AL11" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="AM11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY11" t="n">
         <v>1.15</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.5</v>
       </c>
-      <c r="AR11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="R12" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="S12" t="n">
         <v>1.75</v>
       </c>
       <c r="T12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG12" t="n">
         <v>2.3</v>
       </c>
-      <c r="U12" t="n">
-        <v>8</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AH12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY12" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AZ12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB12" t="n">
         <v>1.18</v>
       </c>
-      <c r="BA12" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="BB12" t="n">
+      <c r="BC12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BF12" t="n">
         <v>1.25</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="R15" t="n">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="S15" t="n">
         <v>2.85</v>
@@ -3386,7 +3386,7 @@
         <v>2.13</v>
       </c>
       <c r="X15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Y15" t="n">
         <v>1.17</v>
@@ -3431,49 +3431,49 @@
         <v>1.5</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="AU15" t="n">
         <v>3.28</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="BB15" t="n">
         <v>1.38</v>
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="R18" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="S18" t="n">
         <v>2.17</v>
@@ -3992,16 +3992,16 @@
         <v>1.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.04</v>
+        <v>3.38</v>
       </c>
       <c r="AE18" t="n">
         <v>2.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
         <v>3.34</v>
@@ -4022,10 +4022,10 @@
         <v>1.73</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4189,7 +4189,7 @@
         <v>1.08</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AD19" t="n">
         <v>2.27</v>
@@ -4201,7 +4201,7 @@
         <v>1.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.9</v>
+        <v>5.15</v>
       </c>
       <c r="AH19" t="n">
         <v>1.1</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -998,130 +998,130 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="R3" t="n">
-        <v>13</v>
+        <v>9.9</v>
       </c>
       <c r="S3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="T3" t="n">
         <v>2.84</v>
       </c>
       <c r="U3" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="X3" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AB3" t="n">
         <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AF3" t="n">
         <v>2.87</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AM3" t="n">
         <v>1.05</v>
       </c>
       <c r="AN3" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="BF3" t="n">
         <v>1.36</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="Q4" t="n">
         <v>3.15</v>
       </c>
       <c r="R4" t="n">
-        <v>2.61</v>
+        <v>2.29</v>
       </c>
       <c r="S4" t="n">
         <v>3.45</v>
@@ -1395,10 +1395,10 @@
         <v>1.31</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.65</v>
+        <v>5.3</v>
       </c>
       <c r="R5" t="n">
-        <v>7.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>1.74</v>
@@ -1434,13 +1434,13 @@
         <v>1.22</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AG5" t="n">
         <v>2.77</v>
@@ -1449,7 +1449,7 @@
         <v>1.39</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.12</v>
@@ -1512,7 +1512,7 @@
         <v>1.89</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="BE5" t="n">
         <v>1.84</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,112 +1589,112 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.78</v>
+        <v>1.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
-        <v>2.23</v>
+        <v>3.35</v>
       </c>
       <c r="S6" t="n">
-        <v>4.03</v>
+        <v>2.26</v>
       </c>
       <c r="T6" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="U6" t="n">
-        <v>2.58</v>
+        <v>4.95</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="X6" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.75</v>
+        <v>6.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.25</v>
+        <v>5.7</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.67</v>
+        <v>1.21</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.46</v>
+        <v>1.96</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.13</v>
+        <v>1.52</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.31</v>
+        <v>1.91</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.74</v>
+        <v>3.12</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.95</v>
+        <v>3.46</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.48</v>
+        <v>5.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.39</v>
+        <v>2.32</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.95</v>
+        <v>1.79</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.76</v>
+        <v>1.22</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.45</v>
+        <v>1.08</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -1706,16 +1706,16 @@
         <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.17</v>
+        <v>1.99</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,112 +1983,112 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>2.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="S8" t="n">
-        <v>2.27</v>
+        <v>4.03</v>
       </c>
       <c r="T8" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="U8" t="n">
-        <v>4.9</v>
+        <v>2.58</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="X8" t="n">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.3</v>
+        <v>6.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AH8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>1.31</v>
       </c>
-      <c r="AI8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN8" t="n">
+      <c r="AR8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS8" t="n">
         <v>1.95</v>
       </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -2100,16 +2100,16 @@
         <v>1.22</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2198,16 +2198,16 @@
         <v>3.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="W9" t="n">
         <v>2.02</v>
       </c>
       <c r="X9" t="n">
-        <v>4.45</v>
+        <v>3.95</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
         <v>12</v>
@@ -2216,7 +2216,7 @@
         <v>1.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AC9" t="n">
         <v>1.77</v>
@@ -2228,7 +2228,7 @@
         <v>3.28</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AG9" t="n">
         <v>6.7</v>
@@ -2243,10 +2243,10 @@
         <v>1.01</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AM9" t="n">
         <v>1.44</v>
@@ -2261,7 +2261,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AR9" t="n">
         <v>2.35</v>
@@ -2279,7 +2279,7 @@
         <v>1.87</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AX9" t="n">
         <v>1.26</v>
@@ -2306,7 +2306,7 @@
         <v>1.29</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="R10" t="n">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="S10" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="T10" t="n">
         <v>2.3</v>
       </c>
       <c r="U10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z10" t="n">
         <v>8</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>6.15</v>
-      </c>
       <c r="AA10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AC10" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AM10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY10" t="n">
         <v>1.15</v>
       </c>
-      <c r="AN10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.75</v>
+        <v>4.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>6</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AR11" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.9</v>
+        <v>2.32</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.82</v>
+        <v>3.02</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.66</v>
+        <v>3.23</v>
       </c>
       <c r="AV11" t="n">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.42</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="R12" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="S12" t="n">
         <v>1.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>3.66</v>
+        <v>2.97</v>
       </c>
       <c r="X12" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AL12" t="n">
         <v>1.63</v>
       </c>
-      <c r="Z12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="AM12" t="n">
         <v>1.15</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM12" t="n">
+      <c r="AN12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF12" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3165,16 +3165,16 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
         <v>2.79</v>
       </c>
       <c r="S14" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="T14" t="n">
         <v>1.95</v>
@@ -3183,7 +3183,7 @@
         <v>3.5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W14" t="n">
         <v>2.17</v>
@@ -3192,7 +3192,7 @@
         <v>3.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
         <v>9.300000000000001</v>
@@ -3201,16 +3201,16 @@
         <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="AF14" t="n">
         <v>1.44</v>
@@ -3228,13 +3228,13 @@
         <v>1.04</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AL14" t="n">
         <v>1.67</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AN14" t="n">
         <v>1.44</v>
@@ -3368,10 +3368,10 @@
         <v>2.87</v>
       </c>
       <c r="R15" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="S15" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="T15" t="n">
         <v>1.82</v>
@@ -3401,19 +3401,19 @@
         <v>1.13</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AG15" t="n">
-        <v>5.93</v>
+        <v>5.92</v>
       </c>
       <c r="AH15" t="n">
         <v>1.07</v>
@@ -3428,13 +3428,13 @@
         <v>2.3</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AM15" t="n">
         <v>1.36</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3443,16 +3443,16 @@
         <v>1.24</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AR15" t="n">
         <v>1.84</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="AU15" t="n">
         <v>3.28</v>
@@ -3464,10 +3464,10 @@
         <v>1.86</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AZ15" t="n">
         <v>1.73</v>
@@ -3485,10 +3485,10 @@
         <v>2.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3756,28 +3756,28 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="Q17" t="n">
         <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>4.33</v>
+        <v>4.96</v>
       </c>
       <c r="S17" t="n">
         <v>2.4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
         <v>5.95</v>
       </c>
       <c r="V17" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W17" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="X17" t="n">
         <v>2.75</v>
@@ -3786,7 +3786,7 @@
         <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AA17" t="n">
         <v>1.04</v>
@@ -3795,19 +3795,19 @@
         <v>1.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AH17" t="n">
         <v>1.25</v>
@@ -3956,10 +3956,10 @@
         <v>1.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="R18" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="S18" t="n">
         <v>2.17</v>
@@ -3974,7 +3974,7 @@
         <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>2.41</v>
+        <v>2.87</v>
       </c>
       <c r="X18" t="n">
         <v>2.8</v>
@@ -3995,7 +3995,7 @@
         <v>1.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.38</v>
+        <v>3.04</v>
       </c>
       <c r="AE18" t="n">
         <v>2.12</v>
@@ -4022,10 +4022,10 @@
         <v>1.73</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4040,7 +4040,7 @@
         <v>1.74</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AT18" t="n">
         <v>2.98</v>
@@ -4055,7 +4055,7 @@
         <v>1.92</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AY18" t="n">
         <v>1.31</v>
@@ -4070,7 +4070,7 @@
         <v>1.22</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.33</v>
+        <v>2.13</v>
       </c>
       <c r="BD18" t="n">
         <v>3.5</v>
@@ -4150,34 +4150,34 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="S19" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="T19" t="n">
         <v>1.82</v>
       </c>
       <c r="U19" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="V19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W19" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X19" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
         <v>10.5</v>
@@ -4189,10 +4189,10 @@
         <v>1.08</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AE19" t="n">
         <v>2.62</v>
@@ -4201,10 +4201,10 @@
         <v>1.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>5.15</v>
+        <v>5.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AI19" t="n">
         <v>12</v>
@@ -4216,10 +4216,10 @@
         <v>2.24</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AN19" t="n">
         <v>1.65</v>
@@ -4264,13 +4264,13 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="BC19" t="n">
         <v>2.65</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="BE19" t="n">
         <v>1.36</v>
@@ -4371,7 +4371,7 @@
         <v>4</v>
       </c>
       <c r="X20" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Y20" t="n">
         <v>1.68</v>
@@ -4395,13 +4395,13 @@
         <v>1.41</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="AG20" t="n">
         <v>2.01</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AI20" t="n">
         <v>3.45</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -804,31 +804,31 @@
         <v>19</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="S2" t="n">
-        <v>7.75</v>
+        <v>12.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W2" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="X2" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Z2" t="n">
         <v>4.2</v>
@@ -843,70 +843,70 @@
         <v>1.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AE2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
         <v>1.44</v>
       </c>
-      <c r="AF2" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AQ2" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.17</v>
+        <v>2.77</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.43</v>
+        <v>3.08</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.3</v>
+        <v>4.49</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.18</v>
+        <v>2.52</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AW2" t="n">
         <v>1.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -918,16 +918,16 @@
         <v>1.11</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BD2" t="n">
         <v>5.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1198,7 +1198,7 @@
         <v>2.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
         <v>2.29</v>
@@ -1207,67 +1207,67 @@
         <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U4" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W4" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="X4" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AH4" t="n">
         <v>1.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AM4" t="n">
         <v>1.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AR4" t="n">
         <v>2.73</v>
@@ -1291,7 +1291,7 @@
         <v>2.55</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AW4" t="n">
         <v>1.56</v>
@@ -1309,16 +1309,16 @@
         <v>2.06</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="BF4" t="n">
         <v>1.08</v>
@@ -1395,19 +1395,19 @@
         <v>1.31</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="R5" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S5" t="n">
         <v>1.74</v>
       </c>
       <c r="T5" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="U5" t="n">
-        <v>8.68</v>
+        <v>8.82</v>
       </c>
       <c r="V5" t="n">
         <v>1.3</v>
@@ -1416,10 +1416,10 @@
         <v>3.16</v>
       </c>
       <c r="X5" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z5" t="n">
         <v>5.65</v>
@@ -1434,28 +1434,28 @@
         <v>1.22</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.2</v>
+        <v>4.23</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AF5" t="n">
         <v>2.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="AH5" t="n">
         <v>1.39</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AL5" t="n">
         <v>1.71</v>
@@ -1476,34 +1476,34 @@
         <v>1.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AZ5" t="n">
         <v>1.24</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.7</v>
+        <v>7.65</v>
       </c>
       <c r="BB5" t="n">
         <v>1.15</v>
@@ -1512,10 +1512,10 @@
         <v>1.89</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BF5" t="n">
         <v>1.21</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,112 +1589,112 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>3.35</v>
+        <v>2.15</v>
       </c>
       <c r="S6" t="n">
-        <v>2.26</v>
+        <v>4.03</v>
       </c>
       <c r="T6" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="U6" t="n">
-        <v>4.95</v>
+        <v>2.58</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="X6" t="n">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.3</v>
+        <v>6.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AH6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>1.31</v>
       </c>
-      <c r="AI6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AR6" t="n">
-        <v>3.12</v>
+        <v>1.74</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.46</v>
+        <v>1.95</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.2</v>
+        <v>2.48</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.32</v>
+        <v>4.39</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.79</v>
+        <v>2.95</v>
       </c>
       <c r="AW6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY6" t="n">
         <v>1.45</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.08</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -1706,16 +1706,16 @@
         <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>2.18</v>
+        <v>3.35</v>
       </c>
       <c r="S7" t="n">
-        <v>3.7</v>
+        <v>2.26</v>
       </c>
       <c r="T7" t="n">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="U7" t="n">
-        <v>2.75</v>
+        <v>4.95</v>
       </c>
       <c r="V7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AW7" t="n">
         <v>1.45</v>
       </c>
-      <c r="W7" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AX7" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
         <v>2.15</v>
       </c>
       <c r="S8" t="n">
-        <v>4.03</v>
+        <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="U8" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="X8" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z8" t="n">
         <v>6.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.29</v>
+        <v>2.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.28</v>
+        <v>3.85</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" t="n">
-        <v>6.25</v>
+        <v>8</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.74</v>
+        <v>2.23</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.95</v>
+        <v>2.49</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.48</v>
+        <v>3.41</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.39</v>
+        <v>3.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.95</v>
+        <v>2.16</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.76</v>
+        <v>1.45</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.7</v>
+        <v>2.86</v>
       </c>
       <c r="R10" t="n">
-        <v>5.75</v>
+        <v>1.9</v>
       </c>
       <c r="S10" t="n">
-        <v>1.94</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>6</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="X10" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA10" t="n">
         <v>1.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="AE10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK10" t="n">
         <v>2.1</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AL10" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="AR10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AU10" t="n">
         <v>2.17</v>
       </c>
-      <c r="AS10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.66</v>
-      </c>
       <c r="AV10" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.24</v>
+        <v>2.62</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.7</v>
+        <v>1.63</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.31</v>
       </c>
-      <c r="Q11" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="V11" t="n">
+      <c r="Z11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.22</v>
       </c>
-      <c r="W11" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="AI11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY11" t="n">
         <v>1.15</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
+      <c r="AZ11" t="n">
         <v>1.24</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="BA11" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.5</v>
       </c>
-      <c r="AR11" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2777,7 +2777,7 @@
         <v>4.9</v>
       </c>
       <c r="R12" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="S12" t="n">
         <v>1.75</v>
@@ -2798,7 +2798,7 @@
         <v>2.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
         <v>6.15</v>
@@ -2810,16 +2810,16 @@
         <v>1.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
         <v>3.1</v>
@@ -2834,10 +2834,10 @@
         <v>1.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AM12" t="n">
         <v>1.15</v>
@@ -2849,16 +2849,16 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.82</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.65</v>
+        <v>3.02</v>
       </c>
       <c r="AT12" t="n">
         <v>4.38</v>
@@ -2867,13 +2867,13 @@
         <v>2.56</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AY12" t="n">
         <v>1.13</v>
@@ -2885,7 +2885,7 @@
         <v>6.75</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BC12" t="n">
         <v>2.05</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.9</v>
+        <v>1.27</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.86</v>
+        <v>4.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.93</v>
+        <v>7.25</v>
       </c>
       <c r="S13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD13" t="n">
         <v>5</v>
       </c>
-      <c r="T13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>1.44</v>
       </c>
-      <c r="AD13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.44</v>
+        <v>2.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>4.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" t="n">
-        <v>10</v>
+        <v>3.54</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.66</v>
+        <v>2.07</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.82</v>
+        <v>2.32</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.89</v>
+        <v>2.75</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.17</v>
+        <v>3.45</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.7</v>
+        <v>2.39</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.38</v>
+        <v>1.89</v>
       </c>
       <c r="AX13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.18</v>
       </c>
-      <c r="AY13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BC13" t="n">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.9</v>
+        <v>1.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.86</v>
+        <v>4.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9</v>
+        <v>8.5</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>2.26</v>
+        <v>2.97</v>
       </c>
       <c r="X10" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>10</v>
+        <v>6.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.56</v>
+        <v>3.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AK10" t="n">
         <v>2.1</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.66</v>
+        <v>2.16</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.82</v>
+        <v>3.02</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.89</v>
+        <v>4.38</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.17</v>
+        <v>2.56</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AX10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>1.18</v>
       </c>
-      <c r="AY10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BA10" t="n">
-        <v>1.63</v>
+        <v>6.75</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.53</v>
+        <v>3.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.7</v>
+        <v>2.86</v>
       </c>
       <c r="R11" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="S11" t="n">
-        <v>1.94</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>6</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="X11" t="n">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA11" t="n">
         <v>1.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="AE11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK11" t="n">
         <v>2.1</v>
       </c>
-      <c r="AF11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AL11" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="AR11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AU11" t="n">
         <v>2.17</v>
       </c>
-      <c r="AS11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.66</v>
-      </c>
       <c r="AV11" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.24</v>
+        <v>2.62</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.26</v>
+        <v>1.63</v>
       </c>
       <c r="BB11" t="n">
         <v>1.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="S12" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="T12" t="n">
         <v>2.3</v>
       </c>
       <c r="U12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z12" t="n">
         <v>8</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>6.15</v>
-      </c>
       <c r="AA12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AC12" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.42</v>
+        <v>2.9</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD12" t="n">
         <v>3.1</v>
       </c>
-      <c r="AH12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY12" t="n">
+      <c r="BE12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF12" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -804,70 +804,70 @@
         <v>19</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.7</v>
+        <v>6.12</v>
       </c>
       <c r="R2" t="n">
         <v>1.1</v>
       </c>
       <c r="S2" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="X2" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AD2" t="n">
         <v>5.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AM2" t="n">
         <v>1.02</v>
@@ -897,7 +897,7 @@
         <v>2.52</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AW2" t="n">
         <v>1.8</v>
@@ -918,16 +918,16 @@
         <v>1.11</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BD2" t="n">
         <v>5.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="R3" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="T3" t="n">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="U3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.81</v>
       </c>
       <c r="V3" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W3" t="n">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="X3" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
         <v>1.18</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.45</v>
+        <v>6</v>
       </c>
       <c r="AE3" t="n">
         <v>1.37</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AL3" t="n">
         <v>1.77</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AN3" t="n">
-        <v>4.2</v>
+        <v>4.93</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1079,52 +1079,52 @@
         <v>1.26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AR3" t="n">
         <v>2.15</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AY3" t="n">
         <v>1.25</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.28</v>
+        <v>8</v>
       </c>
       <c r="BB3" t="n">
         <v>1.09</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,28 +1195,28 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R4" t="n">
-        <v>2.29</v>
+        <v>2.72</v>
       </c>
       <c r="S4" t="n">
         <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U4" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="X4" t="n">
         <v>3.28</v>
@@ -1225,7 +1225,7 @@
         <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="AA4" t="n">
         <v>1.02</v>
@@ -1234,40 +1234,40 @@
         <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.02</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,16 +1309,16 @@
         <v>2.06</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="BF4" t="n">
         <v>1.08</v>
@@ -1392,28 +1392,28 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.25</v>
+        <v>4.65</v>
       </c>
       <c r="R5" t="n">
-        <v>9.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="S5" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="T5" t="n">
         <v>2.37</v>
       </c>
       <c r="U5" t="n">
-        <v>8.82</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="X5" t="n">
         <v>2.47</v>
@@ -1422,43 +1422,43 @@
         <v>1.47</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB5" t="n">
         <v>1.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.23</v>
+        <v>4.06</v>
       </c>
       <c r="AE5" t="n">
         <v>1.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AM5" t="n">
         <v>1.16</v>
@@ -1470,34 +1470,34 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AW5" t="n">
         <v>1.85</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AZ5" t="n">
         <v>1.24</v>
@@ -1506,16 +1506,16 @@
         <v>7.65</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="BF5" t="n">
         <v>1.21</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
         <v>2.15</v>
       </c>
       <c r="S6" t="n">
-        <v>4.03</v>
+        <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="U6" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="X6" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
         <v>6.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.29</v>
+        <v>2.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.28</v>
+        <v>3.85</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.25</v>
+        <v>8</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.74</v>
+        <v>2.23</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.95</v>
+        <v>2.49</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.48</v>
+        <v>3.41</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.39</v>
+        <v>3.1</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.95</v>
+        <v>2.16</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.76</v>
+        <v>1.45</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,112 +1786,112 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>3.35</v>
+        <v>2.15</v>
       </c>
       <c r="S7" t="n">
-        <v>2.26</v>
+        <v>4.03</v>
       </c>
       <c r="T7" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="U7" t="n">
-        <v>4.95</v>
+        <v>2.58</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="X7" t="n">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.3</v>
+        <v>6.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AH7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>1.31</v>
       </c>
-      <c r="AI7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AR7" t="n">
-        <v>3.12</v>
+        <v>1.74</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.46</v>
+        <v>1.95</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.2</v>
+        <v>2.48</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.32</v>
+        <v>4.39</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.79</v>
+        <v>2.95</v>
       </c>
       <c r="AW7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY7" t="n">
         <v>1.45</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.08</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -1903,16 +1903,16 @@
         <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.3</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="R8" t="n">
-        <v>2.15</v>
+        <v>3.79</v>
       </c>
       <c r="S8" t="n">
-        <v>3.7</v>
+        <v>2.28</v>
       </c>
       <c r="T8" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>2.75</v>
+        <v>4.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="X8" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AC8" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE8" t="n">
         <v>1.65</v>
       </c>
-      <c r="AG8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BF8" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.27</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.9</v>
+        <v>2.87</v>
       </c>
       <c r="R10" t="n">
-        <v>8.5</v>
+        <v>1.83</v>
       </c>
       <c r="S10" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
-        <v>2.97</v>
+        <v>2.38</v>
       </c>
       <c r="X10" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.15</v>
+        <v>9</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.42</v>
+        <v>2.43</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.1</v>
+        <v>4.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AK10" t="n">
         <v>2.1</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.16</v>
+        <v>2.66</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.02</v>
+        <v>3.82</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.38</v>
+        <v>5.89</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.56</v>
+        <v>2.17</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.18</v>
+        <v>2.62</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.75</v>
+        <v>1.63</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.9</v>
+        <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.86</v>
+        <v>3.54</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9</v>
+        <v>5.25</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1.94</v>
       </c>
       <c r="T11" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>6</v>
       </c>
       <c r="V11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.55</v>
       </c>
-      <c r="W11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="AI12" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK12" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.9</v>
+        <v>2.32</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.82</v>
+        <v>2.75</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.66</v>
+        <v>3.45</v>
       </c>
       <c r="AV12" t="n">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.26</v>
+        <v>4.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,76 +2968,76 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="R13" t="n">
-        <v>7.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="T13" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>3.66</v>
+        <v>2.88</v>
       </c>
       <c r="X13" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.54</v>
+        <v>5.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AN13" t="n">
         <v>3</v>
@@ -3046,55 +3046,55 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AX13" t="n">
         <v>1.24</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AY13" t="n">
-        <v>1.37</v>
+        <v>1.09</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -784,20 +784,20 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -837,7 +837,7 @@
         <v>1.15</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC2" t="n">
         <v>1.11</v>
@@ -969,32 +969,32 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1181,17 +1181,17 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Q5" t="n">
         <v>4.65</v>
       </c>
       <c r="R5" t="n">
-        <v>7.7</v>
+        <v>10.03</v>
       </c>
       <c r="S5" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="T5" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="U5" t="n">
-        <v>8.699999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>1.31</v>
@@ -1416,13 +1416,13 @@
         <v>3.1</v>
       </c>
       <c r="X5" t="n">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="AA5" t="n">
         <v>1.07</v>
@@ -1434,37 +1434,37 @@
         <v>1.24</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1488,10 +1488,10 @@
         <v>3.42</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AX5" t="n">
         <v>1.53</v>
@@ -1503,22 +1503,22 @@
         <v>1.24</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.65</v>
+        <v>4.65</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
         <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="S7" t="n">
-        <v>4.03</v>
+        <v>3.12</v>
       </c>
       <c r="T7" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="U7" t="n">
-        <v>2.58</v>
+        <v>2.91</v>
       </c>
       <c r="V7" t="n">
         <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="X7" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.75</v>
+        <v>6.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
         <v>1.28</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="AE7" t="n">
         <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1983,28 +1983,28 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="R8" t="n">
-        <v>3.79</v>
+        <v>4.06</v>
       </c>
       <c r="S8" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="U8" t="n">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="X8" t="n">
         <v>2.62</v>
@@ -2022,22 +2022,22 @@
         <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AD8" t="n">
         <v>3.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG8" t="n">
         <v>3.08</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AI8" t="n">
         <v>5.5</v>
@@ -2046,16 +2046,16 @@
         <v>1.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2100,13 +2100,13 @@
         <v>1.25</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BD8" t="n">
         <v>3.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BF8" t="n">
         <v>1.18</v>
@@ -2180,64 +2180,64 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R9" t="n">
         <v>2.62</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T9" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="U9" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="V9" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="W9" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="X9" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
         <v>12</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="AH9" t="n">
         <v>1.06</v>
       </c>
       <c r="AI9" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.01</v>
@@ -2249,40 +2249,40 @@
         <v>1.44</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AR9" t="n">
         <v>2.35</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="AT9" t="n">
         <v>4.73</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AY9" t="n">
         <v>1.1</v>
@@ -2303,10 +2303,10 @@
         <v>2.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Q12" t="n">
         <v>4.7</v>
       </c>
       <c r="R12" t="n">
-        <v>7.25</v>
+        <v>6.9</v>
       </c>
       <c r="S12" t="n">
         <v>1.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="U12" t="n">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
       <c r="V12" t="n">
         <v>1.22</v>
@@ -2795,22 +2795,22 @@
         <v>3.66</v>
       </c>
       <c r="X12" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AB12" t="n">
         <v>1.02</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AD12" t="n">
         <v>5</v>
@@ -2825,19 +2825,19 @@
         <v>2.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AM12" t="n">
         <v>1.17</v>
@@ -2861,10 +2861,10 @@
         <v>2.32</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AV12" t="n">
         <v>2.39</v>
@@ -2876,7 +2876,7 @@
         <v>1.54</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AZ12" t="n">
         <v>1.21</v>
@@ -2885,13 +2885,13 @@
         <v>4.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.6</v>
+        <v>5.15</v>
       </c>
       <c r="BE12" t="n">
         <v>1.91</v>
@@ -3165,16 +3165,16 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="R14" t="n">
         <v>2.79</v>
       </c>
       <c r="S14" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="T14" t="n">
         <v>1.95</v>
@@ -3183,55 +3183,55 @@
         <v>3.5</v>
       </c>
       <c r="V14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC14" t="n">
         <v>1.43</v>
       </c>
-      <c r="W14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AD14" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AI14" t="n">
-        <v>10.5</v>
+        <v>8.1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AM14" t="n">
         <v>1.44</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BC14" t="n">
         <v>2.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3362,130 +3362,130 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="S15" t="n">
-        <v>2.81</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
         <v>1.82</v>
       </c>
       <c r="U15" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="V15" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W15" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="X15" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AA15" t="n">
         <v>1.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AG15" t="n">
-        <v>5.92</v>
+        <v>6.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AI15" t="n">
         <v>11</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.39</v>
+        <v>2.17</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AZ15" t="n">
         <v>1.73</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="BB15" t="n">
         <v>1.38</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="BF15" t="n">
         <v>1.03</v>
@@ -3756,70 +3756,70 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>4.96</v>
+        <v>4.2</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="U17" t="n">
-        <v>5.95</v>
+        <v>4.67</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="X17" t="n">
         <v>2.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.06</v>
       </c>
-      <c r="AC17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK17" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AL17" t="n">
         <v>1.8</v>
@@ -3873,7 +3873,7 @@
         <v>1.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="BD17" t="n">
         <v>3.3</v>
@@ -3953,28 +3953,28 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="R18" t="n">
-        <v>5.5</v>
+        <v>5.15</v>
       </c>
       <c r="S18" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="T18" t="n">
         <v>2.11</v>
       </c>
       <c r="U18" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="V18" t="n">
         <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="X18" t="n">
         <v>2.8</v>
@@ -3983,25 +3983,25 @@
         <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="AE18" t="n">
         <v>2.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
         <v>3.34</v>
@@ -4010,76 +4010,76 @@
         <v>1.24</v>
       </c>
       <c r="AI18" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AR18" t="n">
         <v>1.74</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.52</v>
+        <v>3.78</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AX18" t="n">
         <v>1.65</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AZ18" t="n">
         <v>1.35</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4347,37 +4347,37 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T20" t="n">
         <v>2.41</v>
       </c>
       <c r="U20" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W20" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="X20" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA20" t="n">
         <v>1.18</v>
@@ -4386,40 +4386,40 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.6</v>
+        <v>5.45</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,16 +4464,16 @@
         <v>1.12</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="BD20" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1363,32 +1363,32 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S6" t="n">
         <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U6" t="n">
         <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
         <v>2.5</v>
       </c>
       <c r="X6" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
         <v>6.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
         <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AE6" t="n">
         <v>2.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AH6" t="n">
         <v>1.22</v>
       </c>
       <c r="AI6" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL6" t="n">
         <v>1.83</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         <v>2.49</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="AW6" t="n">
         <v>1.77</v>
@@ -1694,10 +1694,10 @@
         <v>1.45</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BA6" t="n">
         <v>1.89</v>
@@ -1706,16 +1706,16 @@
         <v>1.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,55 +1786,55 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>1.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.35</v>
+        <v>4.06</v>
       </c>
       <c r="S7" t="n">
-        <v>3.12</v>
+        <v>2.15</v>
       </c>
       <c r="T7" t="n">
-        <v>1.98</v>
+        <v>2.24</v>
       </c>
       <c r="U7" t="n">
-        <v>2.91</v>
+        <v>5.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="X7" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG7" t="n">
         <v>3.08</v>
@@ -1843,55 +1843,55 @@
         <v>1.28</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AM7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AX7" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AY7" t="n">
-        <v>1.45</v>
+        <v>1.08</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,55 +1983,55 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>4.06</v>
+        <v>2.35</v>
       </c>
       <c r="S8" t="n">
-        <v>2.15</v>
+        <v>3.12</v>
       </c>
       <c r="T8" t="n">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
-        <v>5.25</v>
+        <v>2.91</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="X8" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
         <v>3.08</v>
@@ -2040,56 +2040,56 @@
         <v>1.28</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.25</v>
+        <v>1.42</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.52</v>
+        <v>1.13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.91</v>
+        <v>1.31</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.12</v>
+        <v>1.74</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.46</v>
+        <v>1.95</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.2</v>
+        <v>2.48</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.32</v>
+        <v>4.39</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.79</v>
+        <v>2.95</v>
       </c>
       <c r="AW8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY8" t="n">
         <v>1.45</v>
       </c>
-      <c r="AX8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.87</v>
+        <v>3.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.83</v>
+        <v>5.34</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1.98</v>
       </c>
       <c r="T10" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>5.75</v>
       </c>
       <c r="V10" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="X10" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="AI10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.09</v>
       </c>
-      <c r="AC10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AK10" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL10" t="n">
         <v>1.62</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.03</v>
+        <v>1.69</v>
       </c>
       <c r="AR10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AU10" t="n">
         <v>2.66</v>
       </c>
-      <c r="AS10" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AV10" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.62</v>
+        <v>1.24</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.63</v>
+        <v>7.26</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.54</v>
+        <v>4.7</v>
       </c>
       <c r="R11" t="n">
-        <v>5.25</v>
+        <v>6.9</v>
       </c>
       <c r="S11" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="T11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AG11" t="n">
         <v>2.3</v>
       </c>
-      <c r="U11" t="n">
-        <v>6</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="AH11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN11" t="n">
         <v>3</v>
       </c>
-      <c r="Y11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC11" t="n">
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY11" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.26</v>
+        <v>4.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.3</v>
+        <v>5.15</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.7</v>
+        <v>4.63</v>
       </c>
       <c r="R12" t="n">
-        <v>6.9</v>
+        <v>6.34</v>
       </c>
       <c r="S12" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>6.1</v>
+        <v>8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>3.66</v>
+        <v>2.88</v>
       </c>
       <c r="X12" t="n">
-        <v>2.36</v>
+        <v>2.73</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AM12" t="n">
+      <c r="BF12" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.37</v>
+        <v>4.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>8.199999999999999</v>
+        <v>1.72</v>
       </c>
       <c r="S13" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="U13" t="n">
-        <v>8</v>
+        <v>2.38</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X13" t="n">
         <v>2.88</v>
       </c>
-      <c r="X13" t="n">
-        <v>2.67</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.5</v>
+        <v>7.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB13" t="n">
         <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AF13" t="n">
         <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AI13" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AM13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN13" t="n">
         <v>1.2</v>
       </c>
-      <c r="AN13" t="n">
-        <v>3</v>
-      </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.77</v>
+        <v>2.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.05</v>
+        <v>2.66</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.35</v>
+        <v>3.82</v>
       </c>
       <c r="AT13" t="n">
-        <v>5</v>
+        <v>5.89</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.2</v>
+        <v>2.62</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.45</v>
+        <v>1.63</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R19" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T19" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="n">
-        <v>5.06</v>
+        <v>5.25</v>
       </c>
       <c r="V19" t="n">
         <v>1.6</v>
       </c>
       <c r="W19" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="X19" t="n">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.09</v>
       </c>
       <c r="AI19" t="n">
         <v>12</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.9</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.8</v>
       </c>
       <c r="V20" t="n">
         <v>1.22</v>
@@ -4371,10 +4371,10 @@
         <v>3.8</v>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="Z20" t="n">
         <v>4.33</v>
@@ -4389,25 +4389,25 @@
         <v>1.11</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AG20" t="n">
         <v>2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" t="n">
         <v>1.38</v>
@@ -4419,7 +4419,7 @@
         <v>1.29</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,16 +4461,16 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BF20" t="n">
         <v>1.36</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1560,32 +1560,32 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1769,20 +1769,20 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2151,32 +2151,32 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2339,19 +2339,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -2360,60 +2360,60 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.75</v>
+        <v>4.63</v>
       </c>
       <c r="R10" t="n">
-        <v>5.34</v>
+        <v>6.34</v>
       </c>
       <c r="S10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="V10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.4</v>
       </c>
-      <c r="W10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z10" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC10" t="n">
         <v>1.3</v>
@@ -2422,88 +2422,88 @@
         <v>3.2</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK10" t="n">
         <v>2.1</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ10" t="n">
+      <c r="AL10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AY10" t="n">
         <v>1.09</v>
       </c>
-      <c r="AK10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.26</v>
+        <v>4.45</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="BD10" t="n">
         <v>3.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -2557,57 +2557,57 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.7</v>
+        <v>4.85</v>
       </c>
       <c r="R11" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="S11" t="n">
         <v>1.75</v>
       </c>
       <c r="T11" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W11" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="X11" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AB11" t="n">
         <v>1.02</v>
@@ -2622,13 +2622,13 @@
         <v>1.44</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="AG11" t="n">
         <v>2.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AI11" t="n">
         <v>3.62</v>
@@ -2637,10 +2637,10 @@
         <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AM11" t="n">
         <v>1.17</v>
@@ -2652,55 +2652,55 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AQ11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX11" t="n">
         <v>1.5</v>
       </c>
-      <c r="AR11" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AY11" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.15</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
         <v>1.91</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,81 +2733,81 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.63</v>
+        <v>3.75</v>
       </c>
       <c r="R12" t="n">
-        <v>6.34</v>
+        <v>5.34</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="U12" t="n">
-        <v>8</v>
+        <v>5.75</v>
       </c>
       <c r="V12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.36</v>
       </c>
-      <c r="W12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z12" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC12" t="n">
         <v>1.3</v>
@@ -2816,88 +2816,88 @@
         <v>3.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="AH12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX12" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI12" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM12" t="n">
+      <c r="AY12" t="n">
         <v>1.15</v>
       </c>
-      <c r="AN12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AX12" t="n">
+      <c r="AZ12" t="n">
         <v>1.24</v>
       </c>
-      <c r="AY12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BA12" t="n">
-        <v>4.45</v>
+        <v>7.26</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BD12" t="n">
         <v>3.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2939,32 +2939,32 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3189,40 +3189,40 @@
         <v>2.4</v>
       </c>
       <c r="X14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Y14" t="n">
         <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="AA14" t="n">
         <v>1.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG14" t="n">
         <v>4.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AI14" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ14" t="n">
         <v>1.05</v>
@@ -3362,61 +3362,61 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="T15" t="n">
         <v>1.82</v>
       </c>
       <c r="U15" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="W15" t="n">
         <v>2.1</v>
       </c>
       <c r="X15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AC15" t="n">
         <v>1.57</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AG15" t="n">
-        <v>6.08</v>
+        <v>5.77</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AI15" t="n">
         <v>11</v>
@@ -3425,25 +3425,25 @@
         <v>1.02</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL15" t="n">
         <v>1.55</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AR15" t="n">
         <v>2</v>
@@ -3452,13 +3452,13 @@
         <v>2.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.17</v>
+        <v>2.37</v>
       </c>
       <c r="AW15" t="n">
         <v>1.72</v>
@@ -3467,7 +3467,7 @@
         <v>1.41</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AZ15" t="n">
         <v>1.73</v>
@@ -3476,19 +3476,19 @@
         <v>2.41</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BC15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD15" t="n">
         <v>2.8</v>
       </c>
-      <c r="BD15" t="n">
-        <v>2.75</v>
-      </c>
       <c r="BE15" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
         <v>2.07</v>
       </c>
       <c r="S16" t="n">
-        <v>4.28</v>
+        <v>3.98</v>
       </c>
       <c r="T16" t="n">
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="V16" t="n">
         <v>1.39</v>
@@ -3583,13 +3583,13 @@
         <v>2.63</v>
       </c>
       <c r="X16" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA16" t="n">
         <v>1.07</v>
@@ -3598,16 +3598,16 @@
         <v>1.02</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AG16" t="n">
         <v>2.92</v>
@@ -3616,22 +3616,22 @@
         <v>1.31</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AM16" t="n">
         <v>1.27</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3756,19 +3756,19 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="Q17" t="n">
         <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>4.2</v>
+        <v>4.95</v>
       </c>
       <c r="S17" t="n">
         <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
         <v>4.67</v>
@@ -3783,40 +3783,40 @@
         <v>2.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AD17" t="n">
         <v>3.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
         <v>3.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AI17" t="n">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK17" t="n">
         <v>1.91</v>
@@ -3873,7 +3873,7 @@
         <v>1.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="BD17" t="n">
         <v>3.3</v>
@@ -3953,22 +3953,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q18" t="n">
         <v>3.5</v>
       </c>
       <c r="R18" t="n">
-        <v>5.15</v>
+        <v>4.97</v>
       </c>
       <c r="S18" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="T18" t="n">
         <v>2.11</v>
       </c>
       <c r="U18" t="n">
-        <v>6.05</v>
+        <v>5.5</v>
       </c>
       <c r="V18" t="n">
         <v>1.36</v>
@@ -3980,7 +3980,7 @@
         <v>2.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z18" t="n">
         <v>7.5</v>
@@ -3989,7 +3989,7 @@
         <v>1.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC18" t="n">
         <v>1.3</v>
@@ -3998,34 +3998,34 @@
         <v>3.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AI18" t="n">
-        <v>7</v>
+        <v>7.06</v>
       </c>
       <c r="AJ18" t="n">
         <v>1.09</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4055,7 +4055,7 @@
         <v>2.1</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AY18" t="n">
         <v>1.35</v>
@@ -4073,7 +4073,7 @@
         <v>2.25</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BE18" t="n">
         <v>1.57</v>
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="U19" t="n">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="V19" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="X19" t="n">
-        <v>3.92</v>
+        <v>3.82</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA19" t="n">
         <v>1.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AI19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BC19" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>

--- a/jogos_2026-03-23.xlsx
+++ b/jogos_2026-03-23.xlsx
@@ -1738,26 +1738,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1769,72 +1769,72 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>4.06</v>
+        <v>2.35</v>
       </c>
       <c r="S7" t="n">
-        <v>2.15</v>
+        <v>3.12</v>
       </c>
       <c r="T7" t="n">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="U7" t="n">
-        <v>5.25</v>
+        <v>2.91</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="X7" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
         <v>3.08</v>
@@ -1843,56 +1843,56 @@
         <v>1.28</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.25</v>
+        <v>1.42</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.52</v>
+        <v>1.13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.91</v>
+        <v>1.31</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.12</v>
+        <v>1.74</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.46</v>
+        <v>1.95</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.2</v>
+        <v>2.48</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.32</v>
+        <v>4.39</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.79</v>
+        <v>2.95</v>
       </c>
       <c r="AW7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY7" t="n">
         <v>1.45</v>
       </c>
-      <c r="AX7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,26 +1935,26 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1966,72 +1966,72 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>1.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.35</v>
+        <v>4.06</v>
       </c>
       <c r="S8" t="n">
-        <v>3.12</v>
+        <v>2.15</v>
       </c>
       <c r="T8" t="n">
-        <v>1.98</v>
+        <v>2.24</v>
       </c>
       <c r="U8" t="n">
-        <v>2.91</v>
+        <v>5.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="X8" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG8" t="n">
         <v>3.08</v>
@@ -2040,55 +2040,55 @@
         <v>1.28</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AM8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AX8" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AY8" t="n">
-        <v>1.45</v>
+        <v>1.08</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2339,81 +2339,81 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N10" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z10" t="n">
         <v>7</v>
       </c>
-      <c r="N10" t="n">
-        <v>3</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>8</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AA10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC10" t="n">
         <v>1.3</v>
@@ -2422,88 +2422,88 @@
         <v>3.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="AH10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX10" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI10" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM10" t="n">
+      <c r="AY10" t="n">
         <v>1.15</v>
       </c>
-      <c r="AN10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AX10" t="n">
+      <c r="AZ10" t="n">
         <v>1.24</v>
       </c>
-      <c r="AY10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BA10" t="n">
-        <v>4.45</v>
+        <v>7.26</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BD10" t="n">
         <v>3.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,37 +2536,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.31</v>
+        <v>4.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.85</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>6.5</v>
+        <v>1.72</v>
       </c>
       <c r="S11" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>5.5</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="X11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AU11" t="n">
         <v>2.17</v>
       </c>
-      <c r="Y11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE11" t="n">
+      <c r="AV11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.44</v>
       </c>
-      <c r="AF11" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,37 +2733,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX12" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R12" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AY12" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="AZ12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BF12" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>7.26</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.11</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,37 +2930,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>4.5</v>
+        <v>1.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>4.63</v>
       </c>
       <c r="R13" t="n">
-        <v>1.72</v>
+        <v>6.34</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>2.38</v>
+        <v>8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="X13" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AB13" t="n">
         <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AI13" t="n">
-        <v>10</v>
+        <v>6.05</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AK13" t="n">
         <v>2.1</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AN13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>1.2</v>
       </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BA13" t="n">
-        <v>1.63</v>
+        <v>4.45</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3136,32 +3136,32 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3351,14 +3351,14 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3548,14 +3548,14 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R17" t="n">
-        <v>4.95</v>
+        <v>4.3</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>4.67</v>
+        <v>4.54</v>
       </c>
       <c r="V17" t="n">
         <v>1.42</v>
@@ -3780,25 +3780,25 @@
         <v>2.62</v>
       </c>
       <c r="X17" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.04</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.06</v>
       </c>
       <c r="AC17" t="n">
         <v>1.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
         <v>2.05</v>
@@ -3807,13 +3807,13 @@
         <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AH17" t="n">
         <v>1.29</v>
       </c>
       <c r="AI17" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AJ17" t="n">
         <v>1.08</v>
@@ -3873,7 +3873,7 @@
         <v>1.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="BD17" t="n">
         <v>3.3</v>
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R18" t="n">
-        <v>4.97</v>
+        <v>4.5</v>
       </c>
       <c r="S18" t="n">
         <v>2.13</v>
@@ -3968,52 +3968,52 @@
         <v>2.11</v>
       </c>
       <c r="U18" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="V18" t="n">
         <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X18" t="n">
         <v>2.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z18" t="n">
         <v>7.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AE18" t="n">
         <v>2.07</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" t="n">
-        <v>7.06</v>
+        <v>6.1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK18" t="n">
         <v>1.85</v>
@@ -4022,64 +4022,64 @@
         <v>1.83</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.78</v>
+        <v>4.86</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AZ18" t="n">
         <v>1.35</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.72</v>
+        <v>3.64</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4150,22 +4150,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="T19" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="U19" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="V19" t="n">
         <v>1.62</v>
@@ -4174,13 +4174,13 @@
         <v>2.16</v>
       </c>
       <c r="X19" t="n">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA19" t="n">
         <v>1.02</v>
@@ -4189,94 +4189,94 @@
         <v>1.11</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AD19" t="n">
         <v>2.25</v>
       </c>
       <c r="AE19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC19" t="n">
         <v>2.8</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="BD19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BE19" t="n">
         <v>1.38</v>
       </c>
-      <c r="AG19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BF19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4347,25 +4347,25 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.8</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.9</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W20" t="n">
         <v>3.8</v>
@@ -4392,10 +4392,10 @@
         <v>5.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AG20" t="n">
         <v>2</v>
@@ -4410,16 +4410,16 @@
         <v>1.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
